--- a/excel_data/Innovation_Fund_Projects_data - 290326.xlsx
+++ b/excel_data/Innovation_Fund_Projects_data - 290326.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zeplatform-my.sharepoint.com/personal/salman_muhammad_zeplatform_eu/Documents/Technical/IF mapping tool/if-map/excel_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="11_1EE5EEA0CB77697A79955972BEC118078624C068" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E804728-1DC7-4448-B46D-9FA694E45A5C}"/>
+  <xr:revisionPtr revIDLastSave="315" documentId="11_1EE5EEA0CB77697A79955972BEC118078624C068" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A8AAA98-E7AA-4932-BF9A-655A14A3F88F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Research</author>
-    <author>tc={F2F13723-C91B-406D-9ECD-FF58B01A16BA}</author>
   </authors>
   <commentList>
     <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
@@ -123,20 +122,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="U2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: €220M (CINEA confirmed, Oct 2024). ACCSION CCS at Aalborg cement plant. Total investment: 'substantial' but not publicly confirmed. Estimate ~€600M (Air Liquide CryocapTM large cement plant CCS, comparable to similar projects). Op: 2029-2030.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="AE2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001C000000}">
       <text>
         <r>
@@ -151,34 +136,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-0000BA000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: €3.17M (CINEA 2020). AGGREGACO2 CCU glass/ceramics Spain. Small pilot. Total investment ~€10M. Op: 2025.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AE3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-0000BB000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant signed (IF20, €3.17M). Cemex + partners. Operational at Alicante, Spain since ~2023-2024. Demonstrating CO₂-negative construction aggregate production at small scale.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="M4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-0000CC000000}">
       <text>
         <r>
@@ -193,20 +150,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-0000CD000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: €97M (CINEA 2021). AIR PtX e-fuels Sweden. Total investment ~€250M est. Op: 2027.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="AE4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-0000CE000000}">
       <text>
         <r>
@@ -249,20 +192,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000042000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: not yet confirmed (IF24 large-scale). AirvaultGoCO₂ Heidelberg Materials CCS France. Total investment ~€600M est. (comparable to VAIA at ~€1.5B - Airvault is smaller at 1 Mt/yr). Op: ~2030.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="AE5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000043000000}">
       <text>
         <r>
@@ -277,62 +206,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="L6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-0000AC000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>AMBASSADOR: Biomethane + CO₂ capture (Poland). Biogenic CO₂ captured from biogas upgrading. No confirmed volume for this project.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-0000AD000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>AMBASSADOR (BZK Energy Poland): Captures biogenic CO₂ from biomethane and fertilizer production. No confirmed volume for this specific Innovation Fund project.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-0000AE000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Estimated: IF23 medium-scale grant (not yet officially published). AMBASSADOR (BZK Energy, Poland) biomethane + CO₂ capture. Estimate ~€35M based on medium-scale project range.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-0000AF000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: not yet confirmed (IF23 medium-scale). AMBASSADOR biomethane+CO₂ capture Poland. Total investment est. ~€80M.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="AE6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-0000B0000000}">
       <text>
         <r>
@@ -347,67 +220,17 @@
         </r>
       </text>
     </comment>
-    <comment ref="B7" authorId="1" shapeId="0" xr:uid="{F2F13723-C91B-406D-9ECD-FF58B01A16BA}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    FYI Anrav has now pulled out and re-applied for IF</t>
-      </text>
-    </comment>
-    <comment ref="U7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000015000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: €189.7M (CINEA confirmed). ANRAV cement CCS, Devnya Bulgaria. Total investment ~€400M est. Op: 2028.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AE7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000016000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant signed (IF21, €189.7M). Devnya Cement (Heidelberg Materials). Permits and engineering ongoing. Storage site characterisation progressing. Operational target: 2028.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Estimated: IF24 large-scale grant, not yet officially published (grant agreement preparation underway, expected H1 2026). Estimate based on comparable IF23 CCS projects (EVEREST: €229M, OLYMPUS: €247M) and ANTHEMIS 0.8 Mt/yr capture scale.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: not yet confirmed (IF24 call - invited to grant agreement preparation Nov 2025). ANTHEMIS oxyfuel CCS. Total investment ~€1B est. Op: 2029.</t>
+    <comment ref="AE7" authorId="0" shapeId="0" xr:uid="{D5A8BB35-3CF3-4489-943F-EC1A2E7E5B7D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Invited to IF24 grant agreement preparation (Nov 2025). Heidelberg Materials France Ciments. FID targeted 2026-2027. Operational target: 2030.</t>
         </r>
       </text>
     </comment>
@@ -425,62 +248,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000067000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>APOLLOCO2-LT: CO₂ hub infrastructure (Greece). No own capture. Hub aggregates CO₂ from regional industrial emitters. Capacity unspecified.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000068000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>APOLLOCO2-LT (Greece): CO₂ Hub infrastructure for collecting, aggregating and distributing CO₂ in Greece. Does not capture CO₂ itself — serves as intermediary for industrial emitters. Hub capacity not publicly specified.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000069000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Estimated: IF24 large-scale grant, not officially published. APOLLOCO2-LT is a CO₂ liquefaction/export hub (infrastructure). Estimate based on stated project CAPEX and the share of €1.26B for large-scale projects.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00006A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: not yet confirmed (IF24 large-scale). APOLLOCO2-LT CO₂ hub Greece. Total investment est. ~€400M+ (large-scale CO₂ hub infrastructure). Op: ~2030.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="AE9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00006B000000}">
       <text>
         <r>
@@ -506,20 +273,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Stated: 7.83 Mt CO₂e removed over first 10 years (Stockholm Exergi docs).</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-0000CA000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Grant: €180M (CINEA 2020). Beccs Stockholm (Stockholm Exergi). Total investment ~€800M+ (FID March 2025; Capsol Technologies contract + infrastructure). Op: 2028.</t>
         </r>
       </text>
     </comment>
@@ -3062,7 +2815,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="604">
   <si>
     <t>EU Innovation Fund — CCS/CCU Project Portfolio Summary</t>
   </si>
@@ -3298,14 +3051,6 @@
 Date</t>
   </si>
   <si>
-    <t>Op.
-Year</t>
-  </si>
-  <si>
-    <t>End
-Year</t>
-  </si>
-  <si>
     <t>Call</t>
   </si>
   <si>
@@ -3515,9 +3260,6 @@
     <t>ANTHEMIS is a large-scale CCS project at Heidelberg Materials’ Antoing cement plant that will deploy a hybrid oxyfuel and amine carbon capture system to capture over 95% of emissions (~800,000 tCO₂/year). The project includes transport and permanent offshore storage, enabling near net-zero cement production from 2029. Invited to IF24 grant agreement preparation (Nov 2025). Amount not confirmed. Permit application submitted H1 2025 for Antoing clinker plant. FID targeted 2026-2027. Operational: 2029.</t>
   </si>
   <si>
-    <t>Hybrid oxyfuel + amine (OxyCal 2nd-gen concept): 98% capture rate; CO₂ via Fluxys Belgium pipeline; North Sea geological storage (Equinor); 0.8 Mt/yr</t>
-  </si>
-  <si>
     <t>Medium-scale</t>
   </si>
   <si>
@@ -3551,9 +3293,6 @@
     <t>ANRAV will establish Eastern Europe’s first full CCS chain, capturing CO₂ from Devnya cement plant and storing it offshore in the Black Sea, achieving ~95% emission reduction.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://climate.ec.europa.eu/document/download/7eb6d2d5-c109-4c33-ba50-c065beb654d7_en?filename=if_pf_2022_anrav_en.pdf </t>
-  </si>
-  <si>
     <t>KOdeCO net zero</t>
   </si>
   <si>
@@ -3584,12 +3323,6 @@
     <t xml:space="preserve"> Aalborg Portland Carbon Capture and Storage using Infrastructure Onshore in North Jutland</t>
   </si>
   <si>
-    <t>Aalborg Portland cement plant; location confirmed.</t>
-  </si>
-  <si>
-    <t>Air Liquide CryocapTM FG (high-pressure cryogenic CO₂ separation) at Aalborg Portland cement plant; CO₂ stored onshore in Aalborg geological formation, North Jutland; 1.4 Mt/yr</t>
-  </si>
-  <si>
     <t>medium-scale</t>
   </si>
   <si>
@@ -3818,9 +3551,6 @@
     <t>Modular 'plug-and-play' post-combustion CO₂ capture at Holcim Martres-Tolosane; industrial test bench for multiple capture technologies; CO₂ pipeline to Pyrenean/Lacq geological storage (Teréga); 700 kt/yr</t>
   </si>
   <si>
-    <t>AirvaultGoCO2</t>
-  </si>
-  <si>
     <t>Industrial CO2 Capture</t>
   </si>
   <si>
@@ -3830,12 +3560,6 @@
     <t>First large-scale CCUS network for deep inland emitters starting from the Europes first zero water intake cement plant</t>
   </si>
   <si>
-    <t>large-scale CO₂ capture at the Heidelberg Materials Airvault cement plant</t>
-  </si>
-  <si>
-    <t>Hybrid post-combustion capture (oxyfuel + calcined clay co-production + 100% waste heat recovery); 95% capture rate; CO₂ pipeline to Saint-Nazaire; ship to North Sea geological storage; 1 Mt/yr; first zero-water-intake cement plant Europe</t>
-  </si>
-  <si>
     <t xml:space="preserve">DEZiR </t>
   </si>
   <si>
@@ -4106,9 +3830,6 @@
     <t>CO2 Hub</t>
   </si>
   <si>
-    <t>DESFA (to verify)</t>
-  </si>
-  <si>
     <t>Revythoussa Island, 19007 Megara, Greece</t>
   </si>
   <si>
@@ -4118,9 +3839,6 @@
     <t>Creation of an innovative and cost-efficient CO2 management solution to heavy industrial emitters through a Liquefaction Export Terminal, leveraging on the CCS hub approach.</t>
   </si>
   <si>
-    <t>Revythoussa terminal project; infrastructure-focused, not a single emitter.</t>
-  </si>
-  <si>
     <t>CO₂ liquefaction export terminal + open-access CCS hub: receives gaseous CO₂ via pipeline from industrial emitters; liquefies using LNG regasification cold energy; CO₂ loaded to ships; South-Eastern European CCS infrastructure hub (DESFA/Hellenic Gas operator)</t>
   </si>
   <si>
@@ -4511,9 +4229,6 @@
     <t>AMBASSADOR</t>
   </si>
   <si>
-    <t>Biomethane production and carbon capture and purification system</t>
-  </si>
-  <si>
     <t>BZK ENERGY SPOLKA Z OGRANICZONA ODPOWIEDZIALNOSCIA</t>
   </si>
   <si>
@@ -4523,12 +4238,6 @@
     <t>Closed-loop installation for sustAinable production of bioMethane, BioCO2 And biofertilizerS a new StandArD fOr zeRo waste economy</t>
   </si>
   <si>
-    <t>Polish CCS project linked to BZK energy; details incomplete.</t>
-  </si>
-  <si>
-    <t>Closed-loop BECCS: biogenic CO₂ captured from biomethane upgrading (PSA/membrane separation) and digestate-based fertiliser production at BZK Energy biogas plant; biomethane to grid; biofertiliser to farms; CO₂ purified for reuse or geological storage</t>
-  </si>
-  <si>
     <t>HuCCSar</t>
   </si>
   <si>
@@ -4568,24 +4277,9 @@
     <t>PETRONOR</t>
   </si>
   <si>
-    <t>Barrio San Martín 5, 48550 Muskiz, Spain</t>
-  </si>
-  <si>
-    <t>Emitter / Utilisation (CCU)</t>
-  </si>
-  <si>
     <t>Fabrication of CO2 negative AGGREGAtes based on disruptive accelerated carbonation processes fuelled by carbon capture in refineries</t>
   </si>
   <si>
-    <t>https://aggregaco2.com/en/</t>
-  </si>
-  <si>
-    <t>AGGREGACO2 will produce carbon-negative aggregates using captured CO₂ and waste residues via accelerated carbonation.</t>
-  </si>
-  <si>
-    <t>Accelerated carbonation CCU: CO₂ captured from Cemex Alicante refinery flue gas + reacted with calcium/magnesium silicate minerals to produce CO₂-negative construction aggregates (permanent CO₂ mineralisation); 2.2 kt/yr pilot</t>
-  </si>
-  <si>
     <t>GREEN MEIGA</t>
   </si>
   <si>
@@ -4670,9 +4364,6 @@
     <t>Maritime CO₂ transport service: medium-pressure liquid CO₂ (LCO₂) vessel with zeolite-based onboard CO₂ capture unit + bioLNG propulsion + innovative boil-off gas management using LNG cold; CO₂ shipped from cement plant to Mediterranean/North Sea geological storage</t>
   </si>
   <si>
-    <t>Beccs Stockholm</t>
-  </si>
-  <si>
     <t>Stockholm Exergi</t>
   </si>
   <si>
@@ -4685,33 +4376,12 @@
     <t>Bio-Energy Carbon Capture and Storage (BECCS) at the existing Combined Heat and Power-plant KVV8 at Värtaverket, Stockholm, Sweden</t>
   </si>
   <si>
-    <t xml:space="preserve">https://cinea.ec.europa.eu/featured-projects/beccs-stockholm-delivering-net-carbon-removals-clean-energy_en </t>
-  </si>
-  <si>
-    <t>BECCS Stockholm will capture biogenic CO₂ from biomass CHP and store it permanently, delivering negative emissions.</t>
-  </si>
-  <si>
     <t>BECCS: Capsol Technologies EcoRP post-combustion amine CO₂ capture on biomass-fired CHP plant (KVV8, Värtaverket); 100% biogenic CO₂; ship transport to offshore North Sea geological storage; negative emission carbon removal; 0.78 Mt/yr</t>
   </si>
   <si>
-    <t>AIR</t>
-  </si>
-  <si>
-    <t>Perstorp Group</t>
-  </si>
-  <si>
     <t>Production of sustainable methanol as raw material for chemical products by first-of-a-kind Carbon Capture and Utilization process integrated with world scale electrolysis unit</t>
   </si>
   <si>
-    <t xml:space="preserve">https://climate.ec.europa.eu/document/download/3167b6b1-0572-42ab-8b03-a9b6108342b4_en?filename=if_pf_2022_air_v5_en.pdf </t>
-  </si>
-  <si>
-    <t>Project Air will produce sustainable methanol using captured CO₂, hydrogen, and biomethane, reducing emissions significantly.</t>
-  </si>
-  <si>
-    <t>CCU e-methanol: post-combustion CO₂ capture from Swedish industrial source + world-scale PEM electrolysis H₂ + methanol synthesis (MeOH); first-of-kind large-scale CCU integrated with world-scale electrolysis; 406 kt/yr CO₂ input</t>
-  </si>
-  <si>
     <t>INNOZHERO</t>
   </si>
   <si>
@@ -4826,10 +4496,151 @@
     <t>E70 Индустриална зона, 9162 Devnya, Bulgaria</t>
   </si>
   <si>
-    <t>Post-combustion amine scrubbing CO₂ capture at Devnya cement plant, Bulgaria; pipeline transport to offshore storage</t>
-  </si>
-  <si>
-    <t>Grant Prep</t>
+    <t>Evaluation End Year</t>
+  </si>
+  <si>
+    <t>ACCSION is a large-scale CCS project at Aalborg Portland’s cement plant in Aalborg, Denmark, developed with Air Liquide to establish an integrated onshore carbon capture, transport, and storage chain. It captures CO₂ from both grey and white cement production using Cryocap™ technology and transports it by pipeline to onshore storage in Denmark. The project will capture about 1.4–1.42 MtCO₂ per year and avoid around 1.5 MtCO₂ annually, including benefits from surplus heat recovery. Around 80 MW of excess heat will be supplied to district heating. The project aims to enable near net-zero scope 1 emissions and demonstrate a scalable CCS model for heavy industry.</t>
+  </si>
+  <si>
+    <t>Capture: Air Liquide Cryocap™ cryogenic CO₂ capture system, capturing CO₂ from flue-gas streams in a single integrated setup.
+Transport: Pipeline transport from the Aalborg cement site to a CO₂ reception/transport infrastructure.
+Storage: Onshore geological storage in Denmark / onshore CO₂ storage facilities (exact final storage formation/site not confirmed).
+Integration notes: renewable electricity supply for the capture plant, certified biogas use in kilns, digital monitoring, and recovery of ~80 MW surplus heat for district heating.</t>
+  </si>
+  <si>
+    <t>BISCAY ECO AGGREGATES, S.L.</t>
+  </si>
+  <si>
+    <t>CO₂ mineralisation plant linked to refinery CO₂ source</t>
+  </si>
+  <si>
+    <t>San Martin 5, Edificio Muñatones, 48550 San Julián de Musques o Somorrostro, Biscay, Spain</t>
+  </si>
+  <si>
+    <t>AGGREGACO2 is a small-scale Innovation Fund project in Spain led by Biscay Eco Aggregates, producing carbon-negative aggregates through CO₂ mineralisation. The project uses CO₂ from the Petronor refinery and reacts it with residues from Energy-from-Waste plants using Accelerated Carbonation Technology. This process converts waste materials into construction aggregates while permanently storing CO₂ as solid carbonates. The facility will process around 22,000 tonnes of residues annually and produce about 56,000 tonnes of aggregates. The project demonstrates circular carbon use by combining industrial CO₂ utilisation with waste valorisation in the construction sector.</t>
+  </si>
+  <si>
+    <t>CO₂ is sourced externally from the Petronor refinery (Steam Methane Reformer flue gas) with no on-site capture, and is transferred over a short distance to the mineralisation facility, where Accelerated Carbonation Technology (ACT, O.C.O Technology) is applied to react CO₂ with air pollution control residues (APCr) from energy-from-waste processes, producing construction aggregates while permanently storing CO₂ as solid carbonates; the system operates at a pilot scale of approximately 2.2 ktCO₂ per year.</t>
+  </si>
+  <si>
+    <t>Operational Year</t>
+  </si>
+  <si>
+    <t>Project Air</t>
+  </si>
+  <si>
+    <t>CCU (e-methanol)</t>
+  </si>
+  <si>
+    <t>Perstorp Oxo AB</t>
+  </si>
+  <si>
+    <t>Perstorp (Stenungsund chemical plant)</t>
+  </si>
+  <si>
+    <t>255 321 000</t>
+  </si>
+  <si>
+    <t>Chemical production (methanol CCU plant)</t>
+  </si>
+  <si>
+    <t>Project Air is a large-scale Innovation Fund project in Stenungsund, Sweden, led by Perstorp Oxo AB, producing sustainable methanol for the chemical industry. It combines captured CO₂ from existing operations with renewable hydrogen from large-scale electrolysis and biomethane to replace fossil-based methanol. The plant will produce around 200,000 tonnes of methanol annually and avoid approximately 4.06 MtCO₂ over ten years. It represents a first-of-a-kind large-scale integration of CCU and Power-to-X in the chemical sector.</t>
+  </si>
+  <si>
+    <t>CO₂ is captured from Perstorp’s existing chemical production processes (industrial point source) and combined with renewable hydrogen produced via a large-scale electrolysis unit powered by renewable electricity, along with biomethane and residue streams, to produce synthesis gas that is converted into methanol via catalytic synthesis; this represents a large-scale CCU Power-to-X system where CO₂ is utilised as a feedstock for sustainable methanol production (~200 kt methanol/year).</t>
+  </si>
+  <si>
+    <t>https://www.perstorp.com/en/about/sustainability/enable/project_air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://aggregaco2.com/en/ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aalborgportland.dk/accsion/ </t>
+  </si>
+  <si>
+    <t>Sanden, 444 84 Stenungsund, Sweden</t>
+  </si>
+  <si>
+    <t>AirvaultGoCO₂</t>
+  </si>
+  <si>
+    <t>CCUS</t>
+  </si>
+  <si>
+    <t>Not confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.heidelbergmaterials.fr/fr/node/523390? </t>
+  </si>
+  <si>
+    <t>Emitter (Cement)</t>
+  </si>
+  <si>
+    <t>AirvaultGOCO₂ is a large-scale CCUS project at Heidelberg Materials’ cement plant in Airvault, France, aiming to capture approximately 1 MtCO₂ per year. The project is part of the GOCO₂ initiative to decarbonise industrial sites in western France by establishing a full CO₂ transport and storage value chain. Captured CO₂ will be transported by pipeline to Saint-Nazaire and shipped to offshore geological storage in the North Sea. A portion of biogenic CO₂ may also be used for e-fuel production. The project is expected to start capturing CO₂ around 2030, subject to funding and regulatory approvals.</t>
+  </si>
+  <si>
+    <t>Post-combustion CO₂ capture at a cement plant (~1 MtCO₂/year planned), with CO₂ transported via pipeline to Saint-Nazaire and then shipped to offshore geological storage in the North Sea; part of the CO₂ stream (biogenic fraction) may be utilised for e-fuel production; final capture technology configuration not yet publicly confirmed.</t>
+  </si>
+  <si>
+    <t>Not Disclosed</t>
+  </si>
+  <si>
+    <t>Bioenergy</t>
+  </si>
+  <si>
+    <t>CCU (biogenic CO₂ capture &amp; purification)</t>
+  </si>
+  <si>
+    <t>AMBASSADOR is a medium-scale Innovation Fund project in Poland led by BZK Energy, developing a closed-loop biogas facility for the production of biomethane, purified CO₂, and biofertilisers. The project integrates anaerobic digestion of agricultural and food waste with gas upgrading and CO₂ capture and liquefaction technologies. Produced biomethane will be injected into the national gas grid, while part of it will be used on-site for energy self-sufficiency. The captured biogenic CO₂ will be purified and reused, contributing to emissions reduction and circular carbon use. Over its first five years of operation, the project is expected to avoid approximately 128 ktCO₂.</t>
+  </si>
+  <si>
+    <t>Closed-loop biogas system with anaerobic digestion of agricultural and food waste, followed by biomethane upgrading (gas purification) and integrated CO₂ capture and liquefaction; biomethane is injected into the gas grid and partially used on-site for energy, while captured biogenic CO₂ is purified for reuse; no geological storage involved (BECCU system).</t>
+  </si>
+  <si>
+    <t>https://bzkenergy.pl/projekt-ambassador/</t>
+  </si>
+  <si>
+    <t>ANRAV is a large-scale CCUS project at the Devnya cement plant in Bulgaria, led by Heidelberg Materials, aiming to capture around 0.8 MtCO₂ per year. The project will establish the first full CCS value chain in Eastern Europe, linking cement production to offshore geological storage in the Black Sea via pipeline infrastructure. Captured CO₂ will be transported to the depleted Galata gas field for permanent storage, while enabling the development of a regional CCUS cluster.</t>
+  </si>
+  <si>
+    <t>https://climate.ec.europa.eu/document/download/7eb6d2d5-c109-4c33-ba50-c065beb654d7_en?filename=if_pf_2022_anrav_en.pdf</t>
+  </si>
+  <si>
+    <t>Hybrid staged CO₂ capture system combining oxyfuel combustion (OxyCal) and post-combustion amine scrubbing. Achieving up to ~99% capture efficiency; CO₂ is processed via a CO₂ Processing Unit (CPU), transported by pipeline, and permanently stored in the depleted Galata gas field under the Black Sea.</t>
+  </si>
+  <si>
+    <t>Not Acquired</t>
+  </si>
+  <si>
+    <t>https://www.anthemis-ccs.com/en/about-the-project</t>
+  </si>
+  <si>
+    <t>Oxyfuel-based CO₂ capture using pure oxygen combustion combined with CO₂ recycling to produce a high-concentration CO₂ stream (&gt;80%), followed by cryogenic purification via a CO₂ Purification Unit (CPU) supplied by Linde to ~98% purity; CO₂ is then transported via pipeline infrastructure operated by Fluxys and connected to the CO₂ Highway Europe system, with offshore geological storage in Norway under development in partnership with Equinor; system designed to capture over 800,000 tCO₂/year.</t>
+  </si>
+  <si>
+    <t>CO₂ transport &amp; storage</t>
+  </si>
+  <si>
+    <t>APOLLOCO2-LT is a large-scale CO₂ infrastructure project in Greece, centred at the Revythoussa LNG terminal and developed to serve as a regional CCS hub. The project aims to aggregate CO₂ from multiple industrial emitters, liquefy it at a dedicated export terminal, and transport it by ship to offshore geological storage sites. It is designed as an open-access system to enable cost-effective CO₂ management for industries across Southeastern Europe. The project leverages existing gas infrastructure and supports the development of a regional CO₂ transport and storage value chain. It has been selected for Innovation Fund 2024 grant agreement preparation.</t>
+  </si>
+  <si>
+    <t>https://www.desfa.gr/en/desfa-secures-e169-3-million-eu-innovation-fund-grant-for-apolloco%E2%82%82-advancing-greeces-first-large-scale-ccs-midstream-infrastructure/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESFA </t>
+  </si>
+  <si>
+    <t>BECCS Stockholm</t>
+  </si>
+  <si>
+    <t>BECCS / Carbon Removal (CDR)</t>
+  </si>
+  <si>
+    <t>BECCS Stockholm is a large-scale carbon removal project developed by Stockholm Exergi at the Värtaverket biomass-fired CHP plant in Sweden. The project will capture approximately 800,000 tonnes of biogenic CO₂ per year using post-combustion carbon capture technology. The captured CO₂ will be liquefied and transported by ship to offshore geological storage sites for permanent sequestration. As the CO₂ originates from biomass, the project delivers negative emissions and contributes to long-term carbon removal. It is one of Europe’s flagship BECCS projects and has received funding from the Innovation Fund 2020.</t>
+  </si>
+  <si>
+    <t>https://www.stockholmexergi.se/en/beccs/</t>
   </si>
 </sst>
 </file>
@@ -4975,7 +4786,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5078,6 +4889,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -5143,7 +4960,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5309,6 +5126,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5378,12 +5202,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Eadbhard Pernot" id="{FA7BE837-65B7-4873-AD78-B15AB3882EC4}" userId="S::eadbhard.pernot@zeplatform.eu::3733c170-1716-4ac4-80e2-f0fad405191d" providerId="AD"/>
-</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5671,14 +5489,6 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B7" dT="2026-03-25T08:53:31.25" personId="{FA7BE837-65B7-4873-AD78-B15AB3882EC4}" id="{F2F13723-C91B-406D-9ECD-FF58B01A16BA}">
-    <text>FYI Anrav has now pulled out and re-applied for IF</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
@@ -5695,40 +5505,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
     </row>
     <row r="4" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
     </row>
     <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -5745,12 +5555,12 @@
       <c r="B6" s="3">
         <v>62</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
@@ -5759,12 +5569,12 @@
       <c r="B7" s="5">
         <v>16</v>
       </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -5773,12 +5583,12 @@
       <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
@@ -5787,12 +5597,12 @@
       <c r="B9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -5801,12 +5611,12 @@
       <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
     </row>
     <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
@@ -5815,12 +5625,12 @@
       <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -5829,24 +5639,24 @@
       <c r="B12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
     </row>
     <row r="15" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="57" t="s">
+      <c r="A15" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
     </row>
     <row r="16" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -5855,14 +5665,14 @@
       <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="64" t="s">
+      <c r="C16" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="61"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="63"/>
     </row>
     <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
@@ -5871,14 +5681,14 @@
       <c r="B17" s="9">
         <v>21</v>
       </c>
-      <c r="C17" s="59" t="s">
+      <c r="C17" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="61"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="63"/>
     </row>
     <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
@@ -5887,14 +5697,14 @@
       <c r="B18" s="11">
         <v>20</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="61"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="63"/>
     </row>
     <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
@@ -5903,14 +5713,14 @@
       <c r="B19" s="13">
         <v>10</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="61"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="63"/>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
@@ -5919,14 +5729,14 @@
       <c r="B20" s="15">
         <v>4</v>
       </c>
-      <c r="C20" s="63" t="s">
+      <c r="C20" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="61"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="63"/>
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
@@ -5935,14 +5745,14 @@
       <c r="B21" s="17">
         <v>3</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="61"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="63"/>
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
@@ -5951,14 +5761,14 @@
       <c r="B22" s="17">
         <v>1</v>
       </c>
-      <c r="C22" s="63" t="s">
+      <c r="C22" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="61"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="63"/>
     </row>
     <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
@@ -5967,14 +5777,14 @@
       <c r="B23" s="17">
         <v>1</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="61"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="63"/>
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
@@ -5983,14 +5793,14 @@
       <c r="B24" s="19">
         <v>1</v>
       </c>
-      <c r="C24" s="63" t="s">
+      <c r="C24" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="60"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="60"/>
-      <c r="H24" s="61"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="63"/>
     </row>
     <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
@@ -5999,26 +5809,26 @@
       <c r="B25" s="21">
         <v>1</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="60"/>
-      <c r="E25" s="60"/>
-      <c r="F25" s="60"/>
-      <c r="G25" s="60"/>
-      <c r="H25" s="61"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="63"/>
     </row>
     <row r="28" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="57" t="s">
+      <c r="A28" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
+      <c r="B28" s="60"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="60"/>
+      <c r="H28" s="60"/>
     </row>
     <row r="29" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
@@ -6271,46 +6081,46 @@
         <v>74</v>
       </c>
       <c r="Q1" s="37" t="s">
+        <v>564</v>
+      </c>
+      <c r="R1" s="37" t="s">
+        <v>556</v>
+      </c>
+      <c r="S1" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="37" t="s">
+      <c r="T1" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="37" t="s">
+      <c r="U1" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="T1" s="37" t="s">
+      <c r="V1" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="U1" s="37" t="s">
+      <c r="W1" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="V1" s="37" t="s">
+      <c r="X1" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="W1" s="37" t="s">
+      <c r="Y1" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="X1" s="37" t="s">
+      <c r="Z1" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="Y1" s="37" t="s">
+      <c r="AA1" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="Z1" s="37" t="s">
+      <c r="AB1" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="AA1" s="37" t="s">
+      <c r="AC1" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="AB1" s="37" t="s">
+      <c r="AD1" s="37" t="s">
         <v>86</v>
-      </c>
-      <c r="AC1" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD1" s="37" t="s">
-        <v>88</v>
       </c>
       <c r="AE1" s="37" t="s">
         <v>18</v>
@@ -6318,27 +6128,27 @@
     </row>
     <row r="2" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H2" s="40">
+        <v>162</v>
+      </c>
+      <c r="H2" s="48">
         <v>1.5</v>
       </c>
       <c r="I2" s="49">
@@ -6348,10 +6158,10 @@
         <v>1.4</v>
       </c>
       <c r="K2" s="49" t="s">
-        <v>95</v>
-      </c>
-      <c r="L2" s="49">
-        <v>15</v>
+        <v>93</v>
+      </c>
+      <c r="L2" s="48">
+        <v>15.077949</v>
       </c>
       <c r="M2" s="49">
         <v>14</v>
@@ -6360,10 +6170,10 @@
         <v>14</v>
       </c>
       <c r="O2" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P2" s="41">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="Q2" s="41">
         <v>2030</v>
@@ -6372,13 +6182,13 @@
         <v>2040</v>
       </c>
       <c r="S2" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T2" s="42">
-        <v>220000000</v>
-      </c>
-      <c r="U2" s="42">
-        <v>600000000</v>
+        <v>220123498</v>
+      </c>
+      <c r="U2" s="42" t="s">
+        <v>584</v>
       </c>
       <c r="V2" s="25">
         <v>57.062100000000001</v>
@@ -6387,23 +6197,25 @@
         <v>9.9770000000000003</v>
       </c>
       <c r="X2" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y2" s="39" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="Z2" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AA2" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB2" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="AB2" s="57" t="s">
+        <v>575</v>
+      </c>
       <c r="AC2" s="39" t="s">
-        <v>169</v>
+        <v>557</v>
       </c>
       <c r="AD2" s="39" t="s">
-        <v>170</v>
+        <v>558</v>
       </c>
       <c r="AE2" s="33" t="s">
         <v>25</v>
@@ -6411,34 +6223,34 @@
     </row>
     <row r="3" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>496</v>
+        <v>559</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="H3" s="44">
-        <v>2.8E-3</v>
-      </c>
-      <c r="I3" s="50">
-        <v>2.2000000000000001E-3</v>
+        <v>482</v>
+      </c>
+      <c r="H3" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="I3" s="50" t="s">
+        <v>93</v>
       </c>
       <c r="J3" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K3" s="50">
         <v>2.2000000000000001E-3</v>
@@ -6446,11 +6258,11 @@
       <c r="L3" s="50">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="M3" s="50">
+      <c r="M3" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="N3" s="50">
         <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="N3" s="50" t="s">
-        <v>95</v>
       </c>
       <c r="O3" s="50">
         <v>2.1999999999999999E-2</v>
@@ -6459,79 +6271,81 @@
         <v>2021</v>
       </c>
       <c r="Q3" s="45">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="R3" s="45">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="S3" s="22" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="T3" s="46">
         <v>3168000</v>
       </c>
-      <c r="U3" s="46">
-        <v>10000000</v>
+      <c r="U3" s="42" t="s">
+        <v>584</v>
       </c>
       <c r="V3" s="29">
-        <v>43.354500000000002</v>
+        <v>43.327720234653299</v>
       </c>
       <c r="W3" s="29">
-        <v>-3.0619999999999998</v>
+        <v>-3.1153158320413699</v>
       </c>
       <c r="X3" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y3" s="43" t="s">
-        <v>497</v>
+        <v>561</v>
       </c>
       <c r="Z3" s="43" t="s">
-        <v>498</v>
+        <v>560</v>
       </c>
       <c r="AA3" s="43" t="s">
-        <v>499</v>
-      </c>
-      <c r="AB3" s="30" t="s">
-        <v>500</v>
+        <v>483</v>
+      </c>
+      <c r="AB3" s="57" t="s">
+        <v>574</v>
       </c>
       <c r="AC3" s="43" t="s">
-        <v>501</v>
+        <v>562</v>
       </c>
       <c r="AD3" s="43" t="s">
-        <v>502</v>
-      </c>
-      <c r="AE3" s="31" t="s">
-        <v>29</v>
+        <v>563</v>
+      </c>
+      <c r="AE3" s="36" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>565</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="28" t="s">
-        <v>539</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>341</v>
-      </c>
       <c r="D4" s="43" t="s">
-        <v>181</v>
+        <v>566</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>58</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="G4" s="4"/>
+        <v>567</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>568</v>
+      </c>
       <c r="H4" s="44">
-        <v>0.40600000000000003</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="50">
         <v>0.40600000000000003</v>
       </c>
       <c r="J4" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K4" s="50">
         <v>0.40600000000000003</v>
@@ -6543,7 +6357,7 @@
         <v>4.0599999999999996</v>
       </c>
       <c r="N4" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O4" s="50">
         <v>4.0599999999999996</v>
@@ -6558,34 +6372,40 @@
         <v>2037</v>
       </c>
       <c r="S4" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T4" s="46">
         <v>97000000</v>
       </c>
-      <c r="U4" s="46">
-        <v>250000000</v>
-      </c>
-      <c r="V4" s="22"/>
-      <c r="W4" s="22"/>
+      <c r="U4" s="46" t="s">
+        <v>569</v>
+      </c>
+      <c r="V4" s="22">
+        <v>58.099057767351503</v>
+      </c>
+      <c r="W4" s="22">
+        <v>11.861499508001399</v>
+      </c>
       <c r="X4" s="22" t="s">
-        <v>383</v>
-      </c>
-      <c r="Y4" s="43"/>
+        <v>372</v>
+      </c>
+      <c r="Y4" s="43" t="s">
+        <v>576</v>
+      </c>
       <c r="Z4" s="43" t="s">
-        <v>384</v>
+        <v>570</v>
       </c>
       <c r="AA4" s="43" t="s">
-        <v>541</v>
-      </c>
-      <c r="AB4" s="30" t="s">
-        <v>542</v>
+        <v>517</v>
+      </c>
+      <c r="AB4" s="57" t="s">
+        <v>573</v>
       </c>
       <c r="AC4" s="43" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="AD4" s="43" t="s">
-        <v>544</v>
+        <v>572</v>
       </c>
       <c r="AE4" s="35" t="s">
         <v>23</v>
@@ -6593,25 +6413,25 @@
     </row>
     <row r="5" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>247</v>
+        <v>577</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>119</v>
+        <v>578</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H5" s="40">
         <v>1</v>
@@ -6623,7 +6443,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L5" s="49">
         <v>10</v>
@@ -6635,10 +6455,10 @@
         <v>10</v>
       </c>
       <c r="O5" s="49" t="s">
-        <v>95</v>
-      </c>
-      <c r="P5" s="41">
-        <v>2025</v>
+        <v>93</v>
+      </c>
+      <c r="P5" s="41" t="s">
+        <v>579</v>
       </c>
       <c r="Q5" s="41">
         <v>2030</v>
@@ -6647,13 +6467,13 @@
         <v>2040</v>
       </c>
       <c r="S5" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T5" s="42">
         <v>170000000</v>
       </c>
-      <c r="U5" s="42">
-        <v>600000000</v>
+      <c r="U5" s="42" t="s">
+        <v>584</v>
       </c>
       <c r="V5" s="25">
         <v>46.809800000000003</v>
@@ -6662,23 +6482,25 @@
         <v>-0.13900000000000001</v>
       </c>
       <c r="X5" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y5" s="39" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="Z5" s="39" t="s">
-        <v>123</v>
+        <v>581</v>
       </c>
       <c r="AA5" s="39" t="s">
-        <v>250</v>
-      </c>
-      <c r="AB5" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="AB5" s="57" t="s">
+        <v>580</v>
+      </c>
       <c r="AC5" s="39" t="s">
-        <v>251</v>
+        <v>582</v>
       </c>
       <c r="AD5" s="39" t="s">
-        <v>252</v>
+        <v>583</v>
       </c>
       <c r="AE5" s="34" t="s">
         <v>21</v>
@@ -6686,32 +6508,50 @@
     </row>
     <row r="6" spans="1:31" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>341</v>
+        <v>585</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>478</v>
+        <v>586</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
+        <v>467</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="H6" s="40">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="I6" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="J6" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="L6" s="49">
+        <v>0.128</v>
+      </c>
+      <c r="M6" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="N6" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="O6" s="44" t="s">
+        <v>93</v>
+      </c>
       <c r="P6" s="41">
         <v>2025</v>
       </c>
@@ -6722,32 +6562,40 @@
         <v>2038</v>
       </c>
       <c r="S6" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T6" s="42">
-        <v>35000000</v>
-      </c>
-      <c r="U6" s="42">
-        <v>80000000</v>
-      </c>
-      <c r="V6" s="23"/>
-      <c r="W6" s="23"/>
+        <v>7958244</v>
+      </c>
+      <c r="U6" s="42" t="s">
+        <v>584</v>
+      </c>
+      <c r="V6" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="W6" s="23" t="s">
+        <v>93</v>
+      </c>
       <c r="X6" s="23" t="s">
-        <v>383</v>
-      </c>
-      <c r="Y6" s="39"/>
+        <v>372</v>
+      </c>
+      <c r="Y6" s="39" t="s">
+        <v>93</v>
+      </c>
       <c r="Z6" s="39" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="AA6" s="39" t="s">
-        <v>481</v>
-      </c>
-      <c r="AB6" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="AB6" s="57" t="s">
+        <v>589</v>
+      </c>
       <c r="AC6" s="39" t="s">
-        <v>482</v>
+        <v>587</v>
       </c>
       <c r="AD6" s="39" t="s">
-        <v>483</v>
+        <v>588</v>
       </c>
       <c r="AE6" s="35" t="s">
         <v>23</v>
@@ -6755,49 +6603,49 @@
     </row>
     <row r="7" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>119</v>
+        <v>578</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H7" s="40">
         <v>0.8</v>
       </c>
-      <c r="I7" s="49">
-        <v>0.6</v>
-      </c>
-      <c r="J7" s="49">
-        <v>0.6</v>
+      <c r="I7" s="40">
+        <v>0.8</v>
+      </c>
+      <c r="J7" s="40">
+        <v>0.8</v>
       </c>
       <c r="K7" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L7" s="49">
         <v>7.8</v>
       </c>
       <c r="M7" s="49">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N7" s="49">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O7" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P7" s="41">
         <v>2023</v>
@@ -6809,13 +6657,13 @@
         <v>2038</v>
       </c>
       <c r="S7" s="23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T7" s="42">
         <v>189694949</v>
       </c>
-      <c r="U7" s="42">
-        <v>400000000</v>
+      <c r="U7" s="42" t="s">
+        <v>584</v>
       </c>
       <c r="V7" s="25">
         <v>43.232830995956597</v>
@@ -6824,51 +6672,51 @@
         <v>27.594387234972402</v>
       </c>
       <c r="X7" s="23" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y7" s="39" t="s">
-        <v>582</v>
+        <v>555</v>
       </c>
       <c r="Z7" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AA7" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB7" s="26" t="s">
-        <v>158</v>
+        <v>154</v>
+      </c>
+      <c r="AB7" s="57" t="s">
+        <v>591</v>
       </c>
       <c r="AC7" s="39" t="s">
-        <v>157</v>
+        <v>590</v>
       </c>
       <c r="AD7" s="39" t="s">
-        <v>583</v>
-      </c>
-      <c r="AE7" s="35" t="s">
-        <v>584</v>
+        <v>592</v>
+      </c>
+      <c r="AE7" s="34" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H8" s="40">
         <v>0.8</v>
@@ -6880,7 +6728,7 @@
         <v>0.8</v>
       </c>
       <c r="K8" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L8" s="49">
         <v>8</v>
@@ -6892,10 +6740,10 @@
         <v>8</v>
       </c>
       <c r="O8" s="49" t="s">
-        <v>95</v>
-      </c>
-      <c r="P8" s="41">
-        <v>2025</v>
+        <v>93</v>
+      </c>
+      <c r="P8" s="41" t="s">
+        <v>579</v>
       </c>
       <c r="Q8" s="41">
         <v>2029</v>
@@ -6904,13 +6752,13 @@
         <v>2039</v>
       </c>
       <c r="S8" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="T8" s="42">
-        <v>200000000</v>
-      </c>
-      <c r="U8" s="42">
-        <v>1000000000</v>
+        <v>140</v>
+      </c>
+      <c r="T8" s="42" t="s">
+        <v>593</v>
+      </c>
+      <c r="U8" s="42" t="s">
+        <v>584</v>
       </c>
       <c r="V8" s="25">
         <v>50.575420999999999</v>
@@ -6919,23 +6767,25 @@
         <v>3.4423240000000002</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y8" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z8" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA8" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB8" s="57" t="s">
+        <v>594</v>
+      </c>
+      <c r="AC8" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="Z8" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA8" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="AB8" s="2"/>
-      <c r="AC8" s="39" t="s">
-        <v>145</v>
-      </c>
       <c r="AD8" s="39" t="s">
-        <v>146</v>
+        <v>595</v>
       </c>
       <c r="AE8" s="34" t="s">
         <v>21</v>
@@ -6943,32 +6793,50 @@
     </row>
     <row r="9" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="B9" s="51" t="s">
-        <v>340</v>
+        <v>137</v>
+      </c>
+      <c r="B9" s="58" t="s">
+        <v>331</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>341</v>
+        <v>596</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>50</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
+        <v>599</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="H9" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="I9" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="K9" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="L9" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="M9" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="N9" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="O9" s="50" t="s">
+        <v>93</v>
+      </c>
       <c r="P9" s="45">
         <v>2025</v>
       </c>
@@ -6979,13 +6847,13 @@
         <v>2040</v>
       </c>
       <c r="S9" s="22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T9" s="46">
-        <v>150000000</v>
-      </c>
-      <c r="U9" s="46">
-        <v>400000000</v>
+        <v>169300000</v>
+      </c>
+      <c r="U9" s="42" t="s">
+        <v>584</v>
       </c>
       <c r="V9" s="29">
         <v>37.981699999999996</v>
@@ -6994,23 +6862,25 @@
         <v>23.365600000000001</v>
       </c>
       <c r="X9" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y9" s="43" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="Z9" s="43" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="AA9" s="43" t="s">
-        <v>346</v>
-      </c>
-      <c r="AB9" s="4"/>
+        <v>336</v>
+      </c>
+      <c r="AB9" s="57" t="s">
+        <v>598</v>
+      </c>
       <c r="AC9" s="43" t="s">
-        <v>347</v>
+        <v>597</v>
       </c>
       <c r="AD9" s="43" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="AE9" s="34" t="s">
         <v>21</v>
@@ -7018,27 +6888,29 @@
     </row>
     <row r="10" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>531</v>
+        <v>600</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>341</v>
+        <v>601</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="H10" s="40"/>
+        <v>512</v>
+      </c>
+      <c r="H10" s="40" t="s">
+        <v>93</v>
+      </c>
       <c r="I10" s="49">
         <v>0.78300000000000003</v>
       </c>
@@ -7046,7 +6918,7 @@
         <v>0.78300000000000003</v>
       </c>
       <c r="K10" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L10" s="49">
         <v>7.83</v>
@@ -7058,7 +6930,7 @@
         <v>7.83</v>
       </c>
       <c r="O10" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P10" s="41">
         <v>2021</v>
@@ -7070,13 +6942,13 @@
         <v>2038</v>
       </c>
       <c r="S10" s="23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="T10" s="42">
         <v>180000000</v>
       </c>
       <c r="U10" s="42">
-        <v>800000000</v>
+        <v>1130000000</v>
       </c>
       <c r="V10" s="25">
         <v>59.361499999999999</v>
@@ -7085,25 +6957,25 @@
         <v>18.103999999999999</v>
       </c>
       <c r="X10" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y10" s="39" t="s">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="Z10" s="39" t="s">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="AA10" s="39" t="s">
-        <v>535</v>
-      </c>
-      <c r="AB10" s="26" t="s">
-        <v>536</v>
+        <v>515</v>
+      </c>
+      <c r="AB10" s="57" t="s">
+        <v>603</v>
       </c>
       <c r="AC10" s="39" t="s">
-        <v>537</v>
+        <v>602</v>
       </c>
       <c r="AD10" s="39" t="s">
-        <v>538</v>
+        <v>516</v>
       </c>
       <c r="AE10" s="36" t="s">
         <v>27</v>
@@ -7111,22 +6983,22 @@
     </row>
     <row r="11" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="40"/>
@@ -7147,7 +7019,7 @@
         <v>2038</v>
       </c>
       <c r="S11" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T11" s="42">
         <v>30000000</v>
@@ -7162,21 +7034,21 @@
         <v>5.3051132660000002</v>
       </c>
       <c r="X11" s="23" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="Y11" s="39"/>
       <c r="Z11" s="39" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="AA11" s="39" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="AB11" s="2"/>
       <c r="AC11" s="39" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="AD11" s="39" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="AE11" s="34" t="s">
         <v>21</v>
@@ -7184,25 +7056,25 @@
     </row>
     <row r="12" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H12" s="44">
         <v>1.3</v>
@@ -7214,7 +7086,7 @@
         <v>1.3</v>
       </c>
       <c r="K12" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L12" s="50">
         <v>13</v>
@@ -7226,7 +7098,7 @@
         <v>13</v>
       </c>
       <c r="O12" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P12" s="45">
         <v>2023</v>
@@ -7238,7 +7110,7 @@
         <v>2038</v>
       </c>
       <c r="S12" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T12" s="46">
         <v>109816528</v>
@@ -7253,25 +7125,25 @@
         <v>9.5841999999999992</v>
       </c>
       <c r="X12" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y12" s="43" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="Z12" s="43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AA12" s="43" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="AB12" s="30" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="AC12" s="43" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="AD12" s="43" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="AE12" s="35" t="s">
         <v>23</v>
@@ -7279,25 +7151,25 @@
     </row>
     <row r="13" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>42</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="H13" s="44">
         <v>0.6</v>
@@ -7309,7 +7181,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L13" s="50">
         <v>5.8</v>
@@ -7321,7 +7193,7 @@
         <v>5.8</v>
       </c>
       <c r="O13" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P13" s="45">
         <v>2023</v>
@@ -7333,7 +7205,7 @@
         <v>2037</v>
       </c>
       <c r="S13" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T13" s="46">
         <v>125198197</v>
@@ -7348,25 +7220,25 @@
         <v>1.7815000000000001</v>
       </c>
       <c r="X13" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y13" s="43" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="Z13" s="43" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AA13" s="43" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AB13" s="30" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AC13" s="43" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AD13" s="43" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="AE13" s="33" t="s">
         <v>25</v>
@@ -7374,25 +7246,25 @@
     </row>
     <row r="14" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D14" s="43" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>56</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="H14" s="44">
         <v>6.4000000000000001E-2</v>
@@ -7404,7 +7276,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="K14" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L14" s="50">
         <v>0.64</v>
@@ -7416,7 +7288,7 @@
         <v>0.64</v>
       </c>
       <c r="O14" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P14" s="45">
         <v>2025</v>
@@ -7428,7 +7300,7 @@
         <v>2038</v>
       </c>
       <c r="S14" s="22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T14" s="46">
         <v>24000000</v>
@@ -7443,23 +7315,23 @@
         <v>11.614000000000001</v>
       </c>
       <c r="X14" s="22" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="Y14" s="43" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="Z14" s="43" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="AA14" s="43" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="AB14" s="4"/>
       <c r="AC14" s="43" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="AD14" s="43" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="AE14" s="35" t="s">
         <v>23</v>
@@ -7467,25 +7339,25 @@
     </row>
     <row r="15" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>42</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H15" s="44">
         <v>0.7</v>
@@ -7497,7 +7369,7 @@
         <v>0.7</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L15" s="50">
         <v>7</v>
@@ -7509,7 +7381,7 @@
         <v>7</v>
       </c>
       <c r="O15" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P15" s="45">
         <v>2024</v>
@@ -7521,7 +7393,7 @@
         <v>2041</v>
       </c>
       <c r="S15" s="22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T15" s="46">
         <v>120000000</v>
@@ -7536,23 +7408,23 @@
         <v>0.99039999999999995</v>
       </c>
       <c r="X15" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y15" s="43" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="Z15" s="43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AA15" s="43"/>
       <c r="AB15" s="30" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AC15" s="43" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="AD15" s="43" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AE15" s="35" t="s">
         <v>23</v>
@@ -7560,25 +7432,25 @@
     </row>
     <row r="16" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>59</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="H16" s="40">
         <v>1</v>
@@ -7590,7 +7462,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L16" s="49">
         <v>10</v>
@@ -7602,7 +7474,7 @@
         <v>10</v>
       </c>
       <c r="O16" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P16" s="41">
         <v>2025</v>
@@ -7614,7 +7486,7 @@
         <v>2042</v>
       </c>
       <c r="S16" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T16" s="42">
         <v>200000000</v>
@@ -7629,21 +7501,21 @@
         <v>25.099062</v>
       </c>
       <c r="X16" s="23" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="Y16" s="39"/>
       <c r="Z16" s="39" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="AA16" s="39" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="AB16" s="2"/>
       <c r="AC16" s="39" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="AD16" s="39" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="AE16" s="34" t="s">
         <v>21</v>
@@ -7651,22 +7523,22 @@
     </row>
     <row r="17" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="40">
@@ -7685,7 +7557,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="O17" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P17" s="41">
         <v>2024</v>
@@ -7697,7 +7569,7 @@
         <v>2031</v>
       </c>
       <c r="S17" s="23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T17" s="42">
         <v>30497000</v>
@@ -7708,23 +7580,23 @@
       <c r="V17" s="23"/>
       <c r="W17" s="23"/>
       <c r="X17" s="23" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="Y17" s="39"/>
       <c r="Z17" s="39" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="AA17" s="39" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="AB17" s="26" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="AC17" s="39" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="AD17" s="39" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="AE17" s="31" t="s">
         <v>33</v>
@@ -7732,25 +7604,25 @@
     </row>
     <row r="18" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="H18" s="40">
         <v>1.3</v>
@@ -7762,7 +7634,7 @@
         <v>1.3</v>
       </c>
       <c r="K18" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L18" s="49">
         <v>13</v>
@@ -7774,7 +7646,7 @@
         <v>13</v>
       </c>
       <c r="O18" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P18" s="41">
         <v>2025</v>
@@ -7786,7 +7658,7 @@
         <v>2038</v>
       </c>
       <c r="S18" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T18" s="42">
         <v>157000000</v>
@@ -7801,25 +7673,25 @@
         <v>13.836399999999999</v>
       </c>
       <c r="X18" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y18" s="39" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="Z18" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AA18" s="39" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="AB18" s="26" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="AC18" s="39" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AD18" s="39" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AE18" s="33" t="s">
         <v>25</v>
@@ -7827,25 +7699,25 @@
     </row>
     <row r="19" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="D19" s="43" t="s">
         <v>106</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" s="43" t="s">
-        <v>108</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H19" s="44">
         <v>0.02</v>
@@ -7854,7 +7726,7 @@
         <v>0.02</v>
       </c>
       <c r="J19" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K19" s="50">
         <v>0.02</v>
@@ -7866,7 +7738,7 @@
         <v>0.2</v>
       </c>
       <c r="N19" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O19" s="50">
         <v>0.2</v>
@@ -7881,7 +7753,7 @@
         <v>2036</v>
       </c>
       <c r="S19" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T19" s="46">
         <v>4265136</v>
@@ -7896,25 +7768,25 @@
         <v>5.359</v>
       </c>
       <c r="X19" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y19" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z19" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA19" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="Z19" s="43" t="s">
+      <c r="AB19" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="AA19" s="43" t="s">
+      <c r="AC19" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="AD19" s="43" t="s">
         <v>114</v>
-      </c>
-      <c r="AB19" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC19" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="AD19" s="43" t="s">
-        <v>116</v>
       </c>
       <c r="AE19" s="31" t="s">
         <v>29</v>
@@ -7922,22 +7794,22 @@
     </row>
     <row r="20" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>49</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="44">
@@ -7950,7 +7822,7 @@
         <v>2.11</v>
       </c>
       <c r="K20" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L20" s="50">
         <v>21.1</v>
@@ -7962,7 +7834,7 @@
         <v>21.1</v>
       </c>
       <c r="O20" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P20" s="45">
         <v>2023</v>
@@ -7974,7 +7846,7 @@
         <v>2036</v>
       </c>
       <c r="S20" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T20" s="46">
         <v>115000000</v>
@@ -7989,25 +7861,25 @@
         <v>-22.0167</v>
       </c>
       <c r="X20" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y20" s="43" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="Z20" s="43" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="AA20" s="43" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="AB20" s="30" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="AC20" s="43" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="AD20" s="43" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="AE20" s="36" t="s">
         <v>27</v>
@@ -8015,25 +7887,25 @@
     </row>
     <row r="21" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>524</v>
+        <v>505</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>525</v>
+        <v>506</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="H21" s="44"/>
       <c r="I21" s="50"/>
@@ -8042,10 +7914,10 @@
       <c r="L21" s="50"/>
       <c r="M21" s="50"/>
       <c r="N21" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O21" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P21" s="45">
         <v>2025</v>
@@ -8057,7 +7929,7 @@
         <v>2039</v>
       </c>
       <c r="S21" s="22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T21" s="46">
         <v>50000000</v>
@@ -8072,23 +7944,23 @@
         <v>2.1794021596499702</v>
       </c>
       <c r="X21" s="22" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y21" s="43" t="s">
-        <v>526</v>
+        <v>507</v>
       </c>
       <c r="Z21" s="43" t="s">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="AA21" s="43" t="s">
-        <v>528</v>
+        <v>509</v>
       </c>
       <c r="AB21" s="4"/>
       <c r="AC21" s="43" t="s">
-        <v>529</v>
+        <v>510</v>
       </c>
       <c r="AD21" s="43" t="s">
-        <v>530</v>
+        <v>511</v>
       </c>
       <c r="AE21" s="34" t="s">
         <v>21</v>
@@ -8096,25 +7968,25 @@
     </row>
     <row r="22" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="H22" s="40">
         <v>1.7904E-2</v>
@@ -8123,7 +7995,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="J22" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K22" s="49">
         <v>1.2999999999999999E-2</v>
@@ -8135,7 +8007,7 @@
         <v>0.13</v>
       </c>
       <c r="N22" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O22" s="49">
         <v>0.13</v>
@@ -8150,7 +8022,7 @@
         <v>2039</v>
       </c>
       <c r="S22" s="23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T22" s="42">
         <v>4150000</v>
@@ -8161,23 +8033,23 @@
       <c r="V22" s="23"/>
       <c r="W22" s="23"/>
       <c r="X22" s="23" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="Y22" s="39"/>
       <c r="Z22" s="39" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="AA22" s="39" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="AB22" s="26" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="AC22" s="39" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="AD22" s="39" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="AE22" s="33" t="s">
         <v>25</v>
@@ -8185,25 +8057,25 @@
     </row>
     <row r="23" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="22" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>57</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="H23" s="44">
         <v>0.05</v>
@@ -8215,7 +8087,7 @@
         <v>0.05</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L23" s="50">
         <v>0.5</v>
@@ -8227,7 +8099,7 @@
         <v>0.5</v>
       </c>
       <c r="O23" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P23" s="45">
         <v>2025</v>
@@ -8239,7 +8111,7 @@
         <v>2037</v>
       </c>
       <c r="S23" s="22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T23" s="46">
         <v>40000000</v>
@@ -8254,23 +8126,23 @@
         <v>18.920000000000002</v>
       </c>
       <c r="X23" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y23" s="43" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="Z23" s="43" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="AA23" s="43" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="AB23" s="4"/>
       <c r="AC23" s="43" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="AD23" s="43" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="AE23" s="35" t="s">
         <v>23</v>
@@ -8278,25 +8150,25 @@
     </row>
     <row r="24" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>42</v>
       </c>
       <c r="F24" s="52" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="G24" s="52" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="H24" s="44">
         <v>0.2</v>
@@ -8305,7 +8177,7 @@
         <v>0.2</v>
       </c>
       <c r="J24" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K24" s="50">
         <v>0.2</v>
@@ -8317,7 +8189,7 @@
         <v>2</v>
       </c>
       <c r="N24" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O24" s="50">
         <v>2</v>
@@ -8332,7 +8204,7 @@
         <v>2039</v>
       </c>
       <c r="S24" s="22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T24" s="46">
         <v>40000000</v>
@@ -8347,23 +8219,23 @@
         <v>1.0189999999999999</v>
       </c>
       <c r="X24" s="22" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="Y24" s="43" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="Z24" s="43" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="AA24" s="43" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AB24" s="4"/>
       <c r="AC24" s="43" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AD24" s="43" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AE24" s="34" t="s">
         <v>21</v>
@@ -8371,22 +8243,22 @@
     </row>
     <row r="25" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>56</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="44">
@@ -8399,7 +8271,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L25" s="50">
         <v>10</v>
@@ -8411,7 +8283,7 @@
         <v>10</v>
       </c>
       <c r="O25" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P25" s="45">
         <v>2025</v>
@@ -8423,7 +8295,7 @@
         <v>2040</v>
       </c>
       <c r="S25" s="22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T25" s="46">
         <v>200000000</v>
@@ -8438,21 +8310,21 @@
         <v>10.329707000000001</v>
       </c>
       <c r="X25" s="22" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="Y25" s="43"/>
       <c r="Z25" s="43" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="AA25" s="43" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AB25" s="4"/>
       <c r="AC25" s="43" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="AD25" s="43" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="AE25" s="34" t="s">
         <v>21</v>
@@ -8460,25 +8332,25 @@
     </row>
     <row r="26" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H26" s="44"/>
       <c r="I26" s="50"/>
@@ -8489,10 +8361,10 @@
       </c>
       <c r="M26" s="50"/>
       <c r="N26" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O26" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P26" s="45">
         <v>2024</v>
@@ -8504,7 +8376,7 @@
         <v>2033</v>
       </c>
       <c r="S26" s="22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T26" s="46">
         <v>40000000</v>
@@ -8515,23 +8387,23 @@
       <c r="V26" s="22"/>
       <c r="W26" s="22"/>
       <c r="X26" s="22" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="Y26" s="43"/>
       <c r="Z26" s="43" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="AA26" s="43" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="AB26" s="30" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="AC26" s="43" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="AD26" s="43" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="AE26" s="33" t="s">
         <v>25</v>
@@ -8539,25 +8411,25 @@
     </row>
     <row r="27" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H27" s="40">
         <v>0.23252429999999999</v>
@@ -8566,7 +8438,7 @@
         <v>0.19500000000000001</v>
       </c>
       <c r="J27" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K27" s="49">
         <v>0.19500000000000001</v>
@@ -8578,7 +8450,7 @@
         <v>1.95</v>
       </c>
       <c r="N27" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O27" s="49">
         <v>1.95</v>
@@ -8593,7 +8465,7 @@
         <v>2038</v>
       </c>
       <c r="S27" s="23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T27" s="42">
         <v>115190750</v>
@@ -8608,25 +8480,25 @@
         <v>4.8125</v>
       </c>
       <c r="X27" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y27" s="39" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="Z27" s="39" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="AA27" s="39" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AB27" s="26" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AC27" s="39" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AD27" s="39" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AE27" s="35" t="s">
         <v>23</v>
@@ -8634,25 +8506,25 @@
     </row>
     <row r="28" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="H28" s="40">
         <v>0.25</v>
@@ -8661,7 +8533,7 @@
         <v>0.25</v>
       </c>
       <c r="J28" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K28" s="49">
         <v>0.25</v>
@@ -8673,7 +8545,7 @@
         <v>2.5</v>
       </c>
       <c r="N28" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O28" s="49">
         <v>2.5</v>
@@ -8688,7 +8560,7 @@
         <v>2038</v>
       </c>
       <c r="S28" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T28" s="42">
         <v>40000000</v>
@@ -8703,23 +8575,23 @@
         <v>11.88</v>
       </c>
       <c r="X28" s="23" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y28" s="39" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="Z28" s="39" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="AA28" s="39" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="AB28" s="2"/>
       <c r="AC28" s="39" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="AD28" s="39" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="AE28" s="34" t="s">
         <v>21</v>
@@ -8727,25 +8599,25 @@
     </row>
     <row r="29" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D29" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="H29" s="40"/>
       <c r="I29" s="49">
@@ -8755,7 +8627,7 @@
         <v>0.93</v>
       </c>
       <c r="K29" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L29" s="49">
         <v>9.3092950000000005</v>
@@ -8767,7 +8639,7 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="O29" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P29" s="41">
         <v>2023</v>
@@ -8779,7 +8651,7 @@
         <v>2039</v>
       </c>
       <c r="S29" s="23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T29" s="42">
         <v>228721666</v>
@@ -8794,25 +8666,25 @@
         <v>7.0148000000000001</v>
       </c>
       <c r="X29" s="23" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="Y29" s="39" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="Z29" s="39" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AA29" s="39" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AB29" s="26" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="AC29" s="39" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="AD29" s="39" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AE29" s="35" t="s">
         <v>23</v>
@@ -8820,25 +8692,25 @@
     </row>
     <row r="30" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D30" s="43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H30" s="44">
         <v>0.7</v>
@@ -8850,7 +8722,7 @@
         <v>0.7</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L30" s="50">
         <v>7</v>
@@ -8862,7 +8734,7 @@
         <v>7</v>
       </c>
       <c r="O30" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P30" s="45">
         <v>2023</v>
@@ -8874,7 +8746,7 @@
         <v>2038</v>
       </c>
       <c r="S30" s="22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T30" s="46">
         <v>191000000</v>
@@ -8889,25 +8761,25 @@
         <v>8.5100999999999996</v>
       </c>
       <c r="X30" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y30" s="43" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="Z30" s="43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AA30" s="43" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AB30" s="30" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AC30" s="43" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="AD30" s="43" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AE30" s="35" t="s">
         <v>23</v>
@@ -8915,25 +8787,25 @@
     </row>
     <row r="31" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>45</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="H31" s="44">
         <v>1</v>
@@ -8945,7 +8817,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L31" s="50">
         <v>10</v>
@@ -8957,7 +8829,7 @@
         <v>10</v>
       </c>
       <c r="O31" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P31" s="45">
         <v>2022</v>
@@ -8969,7 +8841,7 @@
         <v>2037</v>
       </c>
       <c r="S31" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T31" s="46">
         <v>228210004</v>
@@ -8984,25 +8856,25 @@
         <v>17.989599999999999</v>
       </c>
       <c r="X31" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y31" s="43" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="Z31" s="43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AA31" s="43" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="AB31" s="30" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="AC31" s="43" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="AD31" s="43" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="AE31" s="35" t="s">
         <v>23</v>
@@ -9010,25 +8882,25 @@
     </row>
     <row r="32" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B32" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="39" t="s">
         <v>117</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D32" s="39" t="s">
-        <v>119</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H32" s="48">
         <v>1.1000000000000001</v>
@@ -9040,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="K32" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L32" s="49">
         <v>10</v>
@@ -9052,7 +8924,7 @@
         <v>10</v>
       </c>
       <c r="O32" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P32" s="41">
         <v>2023</v>
@@ -9064,7 +8936,7 @@
         <v>2038</v>
       </c>
       <c r="S32" s="23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T32" s="42">
         <v>230000000</v>
@@ -9079,25 +8951,25 @@
         <v>3.9928129999999999</v>
       </c>
       <c r="X32" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y32" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z32" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA32" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="Z32" s="39" t="s">
+      <c r="AB32" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AA32" s="39" t="s">
+      <c r="AC32" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="AB32" s="26" t="s">
+      <c r="AD32" s="39" t="s">
         <v>125</v>
-      </c>
-      <c r="AC32" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="AD32" s="39" t="s">
-        <v>127</v>
       </c>
       <c r="AE32" s="32" t="s">
         <v>37</v>
@@ -9105,22 +8977,22 @@
     </row>
     <row r="33" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>503</v>
+        <v>484</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="40">
@@ -9130,7 +9002,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="J33" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K33" s="49">
         <v>0.28999999999999998</v>
@@ -9142,7 +9014,7 @@
         <v>2.9</v>
       </c>
       <c r="N33" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O33" s="49">
         <v>2.9</v>
@@ -9157,7 +9029,7 @@
         <v>2038</v>
       </c>
       <c r="S33" s="23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T33" s="42">
         <v>122900000</v>
@@ -9168,23 +9040,23 @@
       <c r="V33" s="23"/>
       <c r="W33" s="23"/>
       <c r="X33" s="23" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="Y33" s="39"/>
       <c r="Z33" s="39" t="s">
-        <v>505</v>
+        <v>486</v>
       </c>
       <c r="AA33" s="39" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="AB33" s="26" t="s">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="AC33" s="39" t="s">
-        <v>508</v>
+        <v>489</v>
       </c>
       <c r="AD33" s="39" t="s">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="AE33" s="35" t="s">
         <v>23</v>
@@ -9192,25 +9064,25 @@
     </row>
     <row r="34" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D34" s="39" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>54</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="H34" s="44">
         <v>0.4</v>
@@ -9222,7 +9094,7 @@
         <v>0.4</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L34" s="50">
         <v>8</v>
@@ -9234,7 +9106,7 @@
         <v>4</v>
       </c>
       <c r="O34" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P34" s="45">
         <v>2025</v>
@@ -9246,7 +9118,7 @@
         <v>2036</v>
       </c>
       <c r="S34" s="22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T34" s="46">
         <v>41000000</v>
@@ -9261,23 +9133,23 @@
         <v>8.4393999999999991</v>
       </c>
       <c r="X34" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y34" s="43" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="Z34" s="43" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="AA34" s="43" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="AB34" s="4"/>
       <c r="AC34" s="43" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="AD34" s="43" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="AE34" s="31" t="s">
         <v>31</v>
@@ -9285,25 +9157,25 @@
     </row>
     <row r="35" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B35" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D35" s="43" t="s">
         <v>128</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D35" s="43" t="s">
-        <v>130</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H35" s="44">
         <v>1.7</v>
@@ -9315,7 +9187,7 @@
         <v>1.7</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L35" s="50">
         <v>17</v>
@@ -9327,7 +9199,7 @@
         <v>17</v>
       </c>
       <c r="O35" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P35" s="45">
         <v>2025</v>
@@ -9339,7 +9211,7 @@
         <v>2042</v>
       </c>
       <c r="S35" s="22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T35" s="46">
         <v>159000000</v>
@@ -9354,23 +9226,23 @@
         <v>3.7766611000000001</v>
       </c>
       <c r="X35" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y35" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z35" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA35" s="43" t="s">
         <v>134</v>
-      </c>
-      <c r="Z35" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA35" s="43" t="s">
-        <v>136</v>
       </c>
       <c r="AB35" s="4"/>
       <c r="AC35" s="43" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AD35" s="43" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AE35" s="33" t="s">
         <v>25</v>
@@ -9378,25 +9250,25 @@
     </row>
     <row r="36" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>45</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="H36" s="44"/>
       <c r="I36" s="50"/>
@@ -9416,7 +9288,7 @@
         <v>2035</v>
       </c>
       <c r="S36" s="22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T36" s="46">
         <v>32000000</v>
@@ -9431,23 +9303,23 @@
         <v>18.047000000000001</v>
       </c>
       <c r="X36" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y36" s="43" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="Z36" s="43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AA36" s="43" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="AB36" s="4"/>
       <c r="AC36" s="43" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="AD36" s="43" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="AE36" s="34" t="s">
         <v>21</v>
@@ -9455,25 +9327,25 @@
     </row>
     <row r="37" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>580</v>
+        <v>553</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D37" s="43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>50</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="H37" s="44">
         <v>1.9</v>
@@ -9485,7 +9357,7 @@
         <v>1.9</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L37" s="50">
         <v>19</v>
@@ -9497,7 +9369,7 @@
         <v>19</v>
       </c>
       <c r="O37" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P37" s="45">
         <v>2023</v>
@@ -9509,7 +9381,7 @@
         <v>2039</v>
       </c>
       <c r="S37" s="22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T37" s="46">
         <v>234000000</v>
@@ -9524,25 +9396,25 @@
         <v>23.527000000000001</v>
       </c>
       <c r="X37" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y37" s="43" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="Z37" s="43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AA37" s="43" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="AB37" s="30" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="AC37" s="43" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="AD37" s="43" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="AE37" s="35" t="s">
         <v>23</v>
@@ -9550,22 +9422,22 @@
     </row>
     <row r="38" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>546</v>
+        <v>519</v>
       </c>
       <c r="D38" s="43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>547</v>
+        <v>520</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="40">
@@ -9578,7 +9450,7 @@
         <v>0.2</v>
       </c>
       <c r="K38" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L38" s="49">
         <v>2</v>
@@ -9590,7 +9462,7 @@
         <v>2</v>
       </c>
       <c r="O38" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P38" s="41">
         <v>2025</v>
@@ -9602,7 +9474,7 @@
         <v>2039</v>
       </c>
       <c r="S38" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T38" s="42">
         <v>54000000</v>
@@ -9617,23 +9489,23 @@
         <v>6.7460000000000004</v>
       </c>
       <c r="X38" s="23" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="Y38" s="39" t="s">
-        <v>548</v>
+        <v>521</v>
       </c>
       <c r="Z38" s="39" t="s">
-        <v>549</v>
+        <v>522</v>
       </c>
       <c r="AA38" s="39" t="s">
-        <v>550</v>
+        <v>523</v>
       </c>
       <c r="AB38" s="2"/>
       <c r="AC38" s="39" t="s">
-        <v>551</v>
+        <v>524</v>
       </c>
       <c r="AD38" s="39" t="s">
-        <v>552</v>
+        <v>525</v>
       </c>
       <c r="AE38" s="33" t="s">
         <v>25</v>
@@ -9641,25 +9513,25 @@
     </row>
     <row r="39" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="D39" s="39" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>50</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="H39" s="40">
         <v>0.85799999999999998</v>
@@ -9695,7 +9567,7 @@
         <v>2039</v>
       </c>
       <c r="S39" s="23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T39" s="42">
         <v>127000000</v>
@@ -9710,25 +9582,25 @@
         <v>23.069400000000002</v>
       </c>
       <c r="X39" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y39" s="39" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="Z39" s="39" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="AA39" s="39" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="AB39" s="26" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="AC39" s="39" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AD39" s="39" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="AE39" s="35" t="s">
         <v>23</v>
@@ -9736,25 +9608,25 @@
     </row>
     <row r="40" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B40" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="D40" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H40" s="40">
         <v>1.4</v>
@@ -9766,7 +9638,7 @@
         <v>1.4</v>
       </c>
       <c r="K40" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L40" s="49">
         <v>14</v>
@@ -9778,7 +9650,7 @@
         <v>14</v>
       </c>
       <c r="O40" s="49" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P40" s="41">
         <v>2020</v>
@@ -9790,7 +9662,7 @@
         <v>2035</v>
       </c>
       <c r="S40" s="23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="T40" s="42">
         <v>356900000</v>
@@ -9805,25 +9677,25 @@
         <v>4.2713660000000004</v>
       </c>
       <c r="X40" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y40" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z40" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="Y40" s="39" t="s">
+      <c r="AA40" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="Z40" s="39" t="s">
+      <c r="AB40" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="AA40" s="39" t="s">
+      <c r="AC40" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="AB40" s="26" t="s">
+      <c r="AD40" s="39" t="s">
         <v>102</v>
-      </c>
-      <c r="AC40" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="AD40" s="39" t="s">
-        <v>104</v>
       </c>
       <c r="AE40" s="27" t="s">
         <v>35</v>
@@ -9831,22 +9703,22 @@
     </row>
     <row r="41" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="22" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>553</v>
+        <v>526</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>554</v>
+        <v>527</v>
       </c>
       <c r="D41" s="43" t="s">
-        <v>555</v>
+        <v>528</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>58</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>556</v>
+        <v>529</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="44"/>
@@ -9867,7 +9739,7 @@
         <v>2038</v>
       </c>
       <c r="S41" s="22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T41" s="46">
         <v>29500000</v>
@@ -9878,21 +9750,21 @@
       <c r="V41" s="22"/>
       <c r="W41" s="22"/>
       <c r="X41" s="22" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="Y41" s="43"/>
       <c r="Z41" s="43" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="AA41" s="43" t="s">
-        <v>557</v>
+        <v>530</v>
       </c>
       <c r="AB41" s="4"/>
       <c r="AC41" s="43" t="s">
-        <v>558</v>
+        <v>531</v>
       </c>
       <c r="AD41" s="43" t="s">
-        <v>559</v>
+        <v>532</v>
       </c>
       <c r="AE41" s="33" t="s">
         <v>25</v>
@@ -9900,25 +9772,25 @@
     </row>
     <row r="42" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D42" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>53</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H42" s="44">
         <v>0.36599999999999999</v>
@@ -9930,7 +9802,7 @@
         <v>0.36599999999999999</v>
       </c>
       <c r="K42" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L42" s="50">
         <v>3.66</v>
@@ -9942,7 +9814,7 @@
         <v>3.66</v>
       </c>
       <c r="O42" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P42" s="45">
         <v>2023</v>
@@ -9954,7 +9826,7 @@
         <v>2038</v>
       </c>
       <c r="S42" s="22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T42" s="46">
         <v>117000000</v>
@@ -9969,25 +9841,25 @@
         <v>14.1221</v>
       </c>
       <c r="X42" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y42" s="43" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Z42" s="43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AA42" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB42" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC42" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="AB42" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="AC42" s="43" t="s">
-        <v>163</v>
-      </c>
       <c r="AD42" s="43" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AE42" s="35" t="s">
         <v>23</v>
@@ -9995,22 +9867,22 @@
     </row>
     <row r="43" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="44">
@@ -10023,7 +9895,7 @@
         <v>5</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L43" s="50">
         <v>50</v>
@@ -10035,7 +9907,7 @@
         <v>50</v>
       </c>
       <c r="O43" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P43" s="45">
         <v>2025</v>
@@ -10047,7 +9919,7 @@
         <v>2039</v>
       </c>
       <c r="S43" s="22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T43" s="46">
         <v>118000000</v>
@@ -10062,21 +9934,21 @@
         <v>4.05</v>
       </c>
       <c r="X43" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y43" s="43" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="Z43" s="43" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="AA43" s="43"/>
       <c r="AB43" s="4"/>
       <c r="AC43" s="43" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="AD43" s="43" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="AE43" s="36" t="s">
         <v>27</v>
@@ -10084,25 +9956,25 @@
     </row>
     <row r="44" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="22" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D44" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H44" s="44">
         <v>7.0000000000000007E-2</v>
@@ -10114,7 +9986,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L44" s="50">
         <v>0.7</v>
@@ -10126,7 +9998,7 @@
         <v>0.7</v>
       </c>
       <c r="O44" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P44" s="45">
         <v>2025</v>
@@ -10138,7 +10010,7 @@
         <v>2039</v>
       </c>
       <c r="S44" s="22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T44" s="46">
         <v>45000000</v>
@@ -10153,23 +10025,23 @@
         <v>4.6532999999999998</v>
       </c>
       <c r="X44" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y44" s="43" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Z44" s="43" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AA44" s="43" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="AB44" s="4"/>
       <c r="AC44" s="43" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AD44" s="43" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="AE44" s="34" t="s">
         <v>21</v>
@@ -10177,25 +10049,25 @@
     </row>
     <row r="45" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="23" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D45" s="39" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>47</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="H45" s="40"/>
       <c r="I45" s="49"/>
@@ -10215,7 +10087,7 @@
         <v>2033</v>
       </c>
       <c r="S45" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T45" s="42">
         <v>35000000</v>
@@ -10230,21 +10102,21 @@
         <v>9.6251999999999995</v>
       </c>
       <c r="X45" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y45" s="39"/>
       <c r="Z45" s="39" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="AA45" s="39" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="AB45" s="2"/>
       <c r="AC45" s="39" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="AD45" s="39" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="AE45" s="34" t="s">
         <v>21</v>
@@ -10252,25 +10124,25 @@
     </row>
     <row r="46" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="23" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>581</v>
+        <v>554</v>
       </c>
       <c r="D46" s="43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="H46" s="40">
         <v>0.112</v>
@@ -10282,7 +10154,7 @@
         <v>0.112</v>
       </c>
       <c r="K46" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L46" s="49">
         <v>1.1200000000000001</v>
@@ -10294,7 +10166,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="O46" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P46" s="41">
         <v>2025</v>
@@ -10306,7 +10178,7 @@
         <v>2037</v>
       </c>
       <c r="S46" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T46" s="42">
         <v>31200000</v>
@@ -10321,23 +10193,23 @@
         <v>12.285500000000001</v>
       </c>
       <c r="X46" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y46" s="39" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="Z46" s="39" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="AA46" s="39"/>
       <c r="AB46" s="26" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="AC46" s="39" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="AD46" s="39" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="AE46" s="35" t="s">
         <v>23</v>
@@ -10345,25 +10217,25 @@
     </row>
     <row r="47" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="23" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D47" s="39" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="H47" s="40"/>
       <c r="I47" s="49"/>
@@ -10383,7 +10255,7 @@
         <v>2033</v>
       </c>
       <c r="S47" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T47" s="42">
         <v>38000000</v>
@@ -10398,23 +10270,23 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="X47" s="23" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y47" s="39" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="Z47" s="39" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="AA47" s="39" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="AB47" s="2"/>
       <c r="AC47" s="39" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="AD47" s="39" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="AE47" s="34" t="s">
         <v>21</v>
@@ -10422,22 +10294,22 @@
     </row>
     <row r="48" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="22" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B48" s="28" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="D48" s="43" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="44"/>
@@ -10458,7 +10330,7 @@
         <v>2038</v>
       </c>
       <c r="S48" s="22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T48" s="46">
         <v>35000000</v>
@@ -10469,21 +10341,21 @@
       <c r="V48" s="22"/>
       <c r="W48" s="22"/>
       <c r="X48" s="22" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="Y48" s="43"/>
       <c r="Z48" s="43" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="AA48" s="43" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="AB48" s="4"/>
       <c r="AC48" s="43" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="AD48" s="43" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="AE48" s="35" t="s">
         <v>23</v>
@@ -10491,25 +10363,25 @@
     </row>
     <row r="49" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D49" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>50</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H49" s="40">
         <v>0.7</v>
@@ -10521,7 +10393,7 @@
         <v>0.9</v>
       </c>
       <c r="K49" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L49" s="49">
         <v>6.8</v>
@@ -10533,7 +10405,7 @@
         <v>9</v>
       </c>
       <c r="O49" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P49" s="41">
         <v>2004</v>
@@ -10545,7 +10417,7 @@
         <v>2038</v>
       </c>
       <c r="S49" s="23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T49" s="42">
         <v>247371000</v>
@@ -10560,25 +10432,25 @@
         <v>24.060400000000001</v>
       </c>
       <c r="X49" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y49" s="39" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="Z49" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AA49" s="39" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="AB49" s="26" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AC49" s="39" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="AD49" s="39" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AE49" s="35" t="s">
         <v>23</v>
@@ -10586,25 +10458,25 @@
     </row>
     <row r="50" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H50" s="40"/>
       <c r="I50" s="49"/>
@@ -10624,7 +10496,7 @@
         <v>2038</v>
       </c>
       <c r="S50" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T50" s="42">
         <v>40000000</v>
@@ -10639,23 +10511,23 @@
         <v>24.47278</v>
       </c>
       <c r="X50" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y50" s="39" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="Z50" s="39" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="AA50" s="39" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="AB50" s="2"/>
       <c r="AC50" s="39" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="AD50" s="39" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="AE50" s="34" t="s">
         <v>21</v>
@@ -10663,25 +10535,25 @@
     </row>
     <row r="51" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="22" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B51" s="28" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D51" s="43" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>54</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H51" s="44"/>
       <c r="I51" s="50"/>
@@ -10701,7 +10573,7 @@
         <v>2038</v>
       </c>
       <c r="S51" s="22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T51" s="46">
         <v>55000000</v>
@@ -10716,23 +10588,23 @@
         <v>9.3382000000000005</v>
       </c>
       <c r="X51" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y51" s="43" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="Z51" s="43" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="AA51" s="43" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="AB51" s="4"/>
       <c r="AC51" s="43" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="AD51" s="43" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="AE51" s="34" t="s">
         <v>21</v>
@@ -10741,19 +10613,19 @@
     <row r="52" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="22"/>
       <c r="B52" s="51" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D52" s="43" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="44"/>
@@ -10774,7 +10646,7 @@
         <v>2038</v>
       </c>
       <c r="S52" s="22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T52" s="46">
         <v>62000000</v>
@@ -10789,23 +10661,23 @@
         <v>10.948</v>
       </c>
       <c r="X52" s="22" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y52" s="43" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="Z52" s="43" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="AA52" s="43" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="AB52" s="4"/>
       <c r="AC52" s="43" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="AD52" s="43" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="AE52" s="36" t="s">
         <v>27</v>
@@ -10813,25 +10685,25 @@
     </row>
     <row r="53" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D53" s="39" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="H53" s="40"/>
       <c r="I53" s="49"/>
@@ -10851,7 +10723,7 @@
         <v>2039</v>
       </c>
       <c r="S53" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T53" s="42">
         <v>40000000</v>
@@ -10866,23 +10738,23 @@
         <v>-0.80400000000000005</v>
       </c>
       <c r="X53" s="23" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y53" s="39" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="Z53" s="39" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="AA53" s="39" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="AB53" s="2"/>
       <c r="AC53" s="39" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="AD53" s="39" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="AE53" s="34" t="s">
         <v>21</v>
@@ -10890,25 +10762,25 @@
     </row>
     <row r="54" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B54" s="28" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="H54" s="44">
         <v>0.4</v>
@@ -10920,7 +10792,7 @@
         <v>0.4</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L54" s="50">
         <v>4</v>
@@ -10932,7 +10804,7 @@
         <v>4</v>
       </c>
       <c r="O54" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P54" s="45">
         <v>2022</v>
@@ -10944,7 +10816,7 @@
         <v>2035</v>
       </c>
       <c r="S54" s="22" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="T54" s="46">
         <v>88286266</v>
@@ -10959,25 +10831,25 @@
         <v>25.498100000000001</v>
       </c>
       <c r="X54" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y54" s="43" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="Z54" s="43" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="AA54" s="43" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="AB54" s="30" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="AC54" s="43" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="AD54" s="43" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="AE54" s="33" t="s">
         <v>25</v>
@@ -10985,25 +10857,25 @@
     </row>
     <row r="55" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B55" s="24" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D55" s="39" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="H55" s="40"/>
       <c r="I55" s="49">
@@ -11013,7 +10885,7 @@
         <v>0.04</v>
       </c>
       <c r="K55" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L55" s="49">
         <v>0.15</v>
@@ -11025,7 +10897,7 @@
         <v>0.4</v>
       </c>
       <c r="O55" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P55" s="41">
         <v>2021</v>
@@ -11037,7 +10909,7 @@
         <v>2028</v>
       </c>
       <c r="S55" s="23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="T55" s="42">
         <v>3867988</v>
@@ -11052,25 +10924,25 @@
         <v>-21.401</v>
       </c>
       <c r="X55" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y55" s="39" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="Z55" s="39" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="AA55" s="39" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="AB55" s="26" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="AC55" s="39" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="AD55" s="39" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="AE55" s="31" t="s">
         <v>29</v>
@@ -11078,22 +10950,22 @@
     </row>
     <row r="56" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="23" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="D56" s="39" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="40"/>
@@ -11114,7 +10986,7 @@
         <v>2033</v>
       </c>
       <c r="S56" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T56" s="42">
         <v>35000000</v>
@@ -11129,23 +11001,23 @@
         <v>6.84</v>
       </c>
       <c r="X56" s="23" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y56" s="39" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="Z56" s="39" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="AA56" s="39" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="AB56" s="2"/>
       <c r="AC56" s="39" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="AD56" s="39" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="AE56" s="34" t="s">
         <v>21</v>
@@ -11153,25 +11025,25 @@
     </row>
     <row r="57" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D57" s="39" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H57" s="40">
         <v>4.2750000000000004</v>
@@ -11183,7 +11055,7 @@
         <v>4.2750000000000004</v>
       </c>
       <c r="K57" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L57" s="49">
         <v>42.75</v>
@@ -11195,7 +11067,7 @@
         <v>42.75</v>
       </c>
       <c r="O57" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P57" s="41">
         <v>2025</v>
@@ -11207,7 +11079,7 @@
         <v>2038</v>
       </c>
       <c r="S57" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T57" s="42">
         <v>225000000</v>
@@ -11218,23 +11090,23 @@
       <c r="V57" s="23"/>
       <c r="W57" s="23"/>
       <c r="X57" s="23" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y57" s="39" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="Z57" s="39" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="AA57" s="39"/>
       <c r="AB57" s="26" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="AC57" s="39" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="AD57" s="39" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="AE57" s="33" t="s">
         <v>25</v>
@@ -11242,25 +11114,25 @@
     </row>
     <row r="58" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D58" s="39" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H58" s="40">
         <v>0.1</v>
@@ -11269,7 +11141,7 @@
         <v>0.1</v>
       </c>
       <c r="J58" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K58" s="49">
         <v>0.1</v>
@@ -11281,7 +11153,7 @@
         <v>1</v>
       </c>
       <c r="N58" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O58" s="49">
         <v>1</v>
@@ -11296,7 +11168,7 @@
         <v>2038</v>
       </c>
       <c r="S58" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T58" s="42">
         <v>38000000</v>
@@ -11311,23 +11183,23 @@
         <v>-2.0750000000000002</v>
       </c>
       <c r="X58" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y58" s="39" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="Z58" s="39" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="AA58" s="39" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="AB58" s="2"/>
       <c r="AC58" s="39" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="AD58" s="39" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="AE58" s="34" t="s">
         <v>21</v>
@@ -11335,22 +11207,22 @@
     </row>
     <row r="59" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>516</v>
+        <v>497</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D59" s="39" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>517</v>
+        <v>498</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="40">
@@ -11363,7 +11235,7 @@
         <v>2</v>
       </c>
       <c r="K59" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L59" s="49">
         <v>54</v>
@@ -11375,7 +11247,7 @@
         <v>54</v>
       </c>
       <c r="O59" s="49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P59" s="41">
         <v>2025</v>
@@ -11387,7 +11259,7 @@
         <v>2057</v>
       </c>
       <c r="S59" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T59" s="42">
         <v>205000000</v>
@@ -11402,25 +11274,25 @@
         <v>1.2444999999999999</v>
       </c>
       <c r="X59" s="23" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y59" s="39" t="s">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="Z59" s="39" t="s">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="AA59" s="39" t="s">
-        <v>520</v>
+        <v>501</v>
       </c>
       <c r="AB59" s="26" t="s">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="AC59" s="39" t="s">
-        <v>522</v>
+        <v>503</v>
       </c>
       <c r="AD59" s="39" t="s">
-        <v>523</v>
+        <v>504</v>
       </c>
       <c r="AE59" s="35" t="s">
         <v>23</v>
@@ -11428,25 +11300,25 @@
     </row>
     <row r="60" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D60" s="39" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>50</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="H60" s="40"/>
       <c r="I60" s="49"/>
@@ -11466,7 +11338,7 @@
         <v>2038</v>
       </c>
       <c r="S60" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T60" s="42">
         <v>30000000</v>
@@ -11481,23 +11353,23 @@
         <v>22.896100000000001</v>
       </c>
       <c r="X60" s="23" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y60" s="39" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="Z60" s="39" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="AA60" s="39" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="AB60" s="2"/>
       <c r="AC60" s="39" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="AD60" s="39" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="AE60" s="34" t="s">
         <v>21</v>
@@ -11505,22 +11377,22 @@
     </row>
     <row r="61" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B61" s="28" t="s">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D61" s="43" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="44">
@@ -11530,7 +11402,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="J61" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K61" s="50">
         <v>5.6000000000000001E-2</v>
@@ -11542,7 +11414,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="N61" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O61" s="50">
         <v>0.56000000000000005</v>
@@ -11557,7 +11429,7 @@
         <v>2037</v>
       </c>
       <c r="S61" s="22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T61" s="46">
         <v>49000000</v>
@@ -11568,23 +11440,23 @@
       <c r="V61" s="22"/>
       <c r="W61" s="22"/>
       <c r="X61" s="22" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="Y61" s="43"/>
       <c r="Z61" s="43" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="AA61" s="43" t="s">
-        <v>512</v>
+        <v>493</v>
       </c>
       <c r="AB61" s="30" t="s">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="AC61" s="43" t="s">
-        <v>514</v>
+        <v>495</v>
       </c>
       <c r="AD61" s="43" t="s">
-        <v>515</v>
+        <v>496</v>
       </c>
       <c r="AE61" s="35" t="s">
         <v>23</v>
@@ -11592,25 +11464,25 @@
     </row>
     <row r="62" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B62" s="28" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D62" s="43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>42</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="H62" s="44">
         <v>1.2</v>
@@ -11622,7 +11494,7 @@
         <v>1.2</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L62" s="50">
         <v>12</v>
@@ -11634,7 +11506,7 @@
         <v>12</v>
       </c>
       <c r="O62" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P62" s="45">
         <v>2025</v>
@@ -11646,7 +11518,7 @@
         <v>2040</v>
       </c>
       <c r="S62" s="22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T62" s="46">
         <v>260000000</v>
@@ -11661,23 +11533,23 @@
         <v>5.3994999999999997</v>
       </c>
       <c r="X62" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Y62" s="43" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="Z62" s="43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AA62" s="43" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="AB62" s="4"/>
       <c r="AC62" s="43" t="s">
-        <v>579</v>
+        <v>552</v>
       </c>
       <c r="AD62" s="43" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="AE62" s="34" t="s">
         <v>21</v>
@@ -11685,25 +11557,25 @@
     </row>
     <row r="63" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="22" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B63" s="28" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D63" s="43" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="H63" s="44"/>
       <c r="I63" s="50"/>
@@ -11723,7 +11595,7 @@
         <v>2038</v>
       </c>
       <c r="S63" s="22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T63" s="46">
         <v>35000000</v>
@@ -11738,21 +11610,21 @@
         <v>22.126007672556039</v>
       </c>
       <c r="X63" s="22" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="Y63" s="43"/>
       <c r="Z63" s="43" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="AA63" s="43" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="AB63" s="4"/>
       <c r="AC63" s="43" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="AD63" s="43" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="AE63" s="34" t="s">
         <v>21</v>
@@ -11795,9 +11667,15 @@
     <hyperlink ref="AB59" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
     <hyperlink ref="AB10" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
     <hyperlink ref="AB4" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
+    <hyperlink ref="AB2" r:id="rId31" xr:uid="{0E1C5928-9B93-4E1E-8BD0-FF94A64740CD}"/>
+    <hyperlink ref="AB5" r:id="rId32" xr:uid="{3C3F6C70-0B94-45FA-99F2-810AD88EED6E}"/>
+    <hyperlink ref="AB6" r:id="rId33" xr:uid="{A0C5128B-A85D-437E-9A18-50F3C0F382EE}"/>
+    <hyperlink ref="AB8" r:id="rId34" xr:uid="{B4509738-B075-4F32-B2E7-24E48F20C8A9}"/>
+    <hyperlink ref="AB9" r:id="rId35" xr:uid="{4627E820-933A-4F01-8787-FD24A68A4341}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId31"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId36"/>
+  <legacyDrawing r:id="rId37"/>
 </worksheet>
 </file>
 
@@ -11816,151 +11694,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="71" t="s">
-        <v>560</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
+      <c r="A1" s="73" t="s">
+        <v>533</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="57" t="s">
-        <v>561</v>
-      </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
+      <c r="A3" s="59" t="s">
+        <v>534</v>
+      </c>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="77" t="s">
-        <v>562</v>
-      </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="66" t="s">
-        <v>563</v>
-      </c>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
+      <c r="A4" s="79" t="s">
+        <v>535</v>
+      </c>
+      <c r="B4" s="63"/>
+      <c r="C4" s="68" t="s">
+        <v>536</v>
+      </c>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="66" t="s">
-        <v>564</v>
-      </c>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="68" t="s">
+        <v>537</v>
+      </c>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="66" t="s">
-        <v>565</v>
-      </c>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="68" t="s">
+        <v>538</v>
+      </c>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="66" t="s">
-        <v>566</v>
-      </c>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="68" t="s">
+        <v>539</v>
+      </c>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="66" t="s">
-        <v>567</v>
-      </c>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="68" t="s">
+        <v>540</v>
+      </c>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="69" t="s">
+      <c r="A9" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="66" t="s">
-        <v>568</v>
-      </c>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="68" t="s">
+        <v>541</v>
+      </c>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="67" t="s">
+      <c r="A10" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="66" t="s">
-        <v>569</v>
-      </c>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="68" t="s">
+        <v>542</v>
+      </c>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="57" t="s">
-        <v>570</v>
-      </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
+      <c r="A12" s="59" t="s">
+        <v>543</v>
+      </c>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="68" t="s">
-        <v>571</v>
-      </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="66" t="s">
-        <v>572</v>
-      </c>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
+      <c r="A13" s="70" t="s">
+        <v>544</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="68" t="s">
+        <v>545</v>
+      </c>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="75" t="s">
-        <v>573</v>
-      </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="66" t="s">
-        <v>574</v>
-      </c>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
+      <c r="A14" s="77" t="s">
+        <v>546</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="68" t="s">
+        <v>547</v>
+      </c>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="70" t="s">
-        <v>575</v>
-      </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="66" t="s">
-        <v>576</v>
-      </c>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
+      <c r="A15" s="72" t="s">
+        <v>548</v>
+      </c>
+      <c r="B15" s="63"/>
+      <c r="C15" s="68" t="s">
+        <v>549</v>
+      </c>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="54" t="s">
-        <v>577</v>
+        <v>550</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="53"/>
       <c r="B19" t="s">
-        <v>578</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -12266,10 +12144,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51CBE187-A7DE-4A9A-99BE-7485C92477B0}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="ba695df1-2cef-45b3-b38e-525c8136ab22"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e"/>
-    <ds:schemaRef ds:uri="ba695df1-2cef-45b3-b38e-525c8136ab22"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/excel_data/Innovation_Fund_Projects_data - 290326.xlsx
+++ b/excel_data/Innovation_Fund_Projects_data - 290326.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zeplatform-my.sharepoint.com/personal/salman_muhammad_zeplatform_eu/Documents/Technical/IF mapping tool/if-map/excel_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1135" documentId="11_1EE5EEA0CB77697A79955972BEC118078624C068" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6B93231-2346-4042-A087-EF35E5D7EB37}"/>
+  <xr:revisionPtr revIDLastSave="1165" documentId="11_1EE5EEA0CB77697A79955972BEC118078624C068" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{146DF877-BC1F-44F2-A3E0-7F2FC09CAA4F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1032,20 +1032,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="T45" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000097000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Estimated: IF23 medium-scale grant. MetZero (Norway) biocarbon for metallurgy. Estimate ~€35M. Grant amount not confirmed publicly.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="U45" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000098000000}">
       <text>
         <r>
@@ -1849,7 +1835,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="652">
   <si>
     <t>EU Innovation Fund — CCS/CCU Project Portfolio Summary</t>
   </si>
@@ -2132,9 +2118,6 @@
     <t>Chemicals</t>
   </si>
   <si>
-    <t>CO2 T&amp;S</t>
-  </si>
-  <si>
     <t>Air Liquide</t>
   </si>
   <si>
@@ -2645,9 +2628,6 @@
     <t>Refineries</t>
   </si>
   <si>
-    <t>Hybrid (CCS + CCU)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Motor Oil (Hellas) Corinth Refineries S.A. </t>
   </si>
   <si>
@@ -2706,9 +2686,6 @@
   </si>
   <si>
     <t>Danube Removals</t>
-  </si>
-  <si>
-    <t>Carbon Removal (CDR / BECCS)</t>
   </si>
   <si>
     <t>Carbon Removal (BioCCS)</t>
@@ -3315,9 +3292,6 @@
   </si>
   <si>
     <t>CO₂ storage infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Offshore CO₂ storage </t>
   </si>
   <si>
     <t>https://www.aramislaunchstores.com/</t>
@@ -3837,9 +3811,6 @@
     <t>https://ec.europa.eu/assets/cinea/project_fiches/innovation_fund/101191543.pdf</t>
   </si>
   <si>
-    <t>Biofuels and bio-refineries</t>
-  </si>
-  <si>
     <t>NG Nordic AS</t>
   </si>
   <si>
@@ -3853,6 +3824,9 @@
   </si>
   <si>
     <t>The project converts waste wood and low-value biomass into biocarbon for metallurgical use through pyrolysis followed by agglomeration, producing a biogenic reductant with high carbon density and reactivity suitable for silicon and manganese production. The public fiche states output of 10 kt/year of biocarbon and 36 GWh of carbon-neutral energy, with no direct CO₂ capture, transport or storage step disclosed.</t>
+  </si>
+  <si>
+    <t>Carbon Removal (CDR / BioCCS)</t>
   </si>
 </sst>
 </file>
@@ -3862,7 +3836,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -4357,6 +4331,45 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4408,45 +4421,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4768,40 +4742,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
     </row>
     <row r="4" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
     </row>
     <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -4818,12 +4792,12 @@
       <c r="B6" s="3">
         <v>62</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
@@ -4832,12 +4806,12 @@
       <c r="B7" s="5">
         <v>16</v>
       </c>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -4846,12 +4820,12 @@
       <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
@@ -4860,12 +4834,12 @@
       <c r="B9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -4874,12 +4848,12 @@
       <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
     </row>
     <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
@@ -4888,12 +4862,12 @@
       <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -4902,24 +4876,24 @@
       <c r="B12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
     </row>
     <row r="15" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="56" t="s">
+      <c r="A15" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
+      <c r="B15" s="70"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
     </row>
     <row r="16" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -4928,14 +4902,14 @@
       <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="63" t="s">
+      <c r="C16" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="60"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="73"/>
     </row>
     <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
@@ -4944,14 +4918,14 @@
       <c r="B17" s="9">
         <v>21</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="60"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="73"/>
     </row>
     <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
@@ -4960,14 +4934,14 @@
       <c r="B18" s="11">
         <v>20</v>
       </c>
-      <c r="C18" s="62" t="s">
+      <c r="C18" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="60"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="73"/>
     </row>
     <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
@@ -4976,14 +4950,14 @@
       <c r="B19" s="13">
         <v>10</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="60"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="73"/>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
@@ -4992,14 +4966,14 @@
       <c r="B20" s="15">
         <v>4</v>
       </c>
-      <c r="C20" s="62" t="s">
+      <c r="C20" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="60"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="73"/>
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
@@ -5008,14 +4982,14 @@
       <c r="B21" s="17">
         <v>3</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="60"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="73"/>
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
@@ -5024,14 +4998,14 @@
       <c r="B22" s="17">
         <v>1</v>
       </c>
-      <c r="C22" s="62" t="s">
+      <c r="C22" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="60"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="73"/>
     </row>
     <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
@@ -5040,14 +5014,14 @@
       <c r="B23" s="17">
         <v>1</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="60"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="73"/>
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
@@ -5056,14 +5030,14 @@
       <c r="B24" s="19">
         <v>1</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="60"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="73"/>
     </row>
     <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
@@ -5072,26 +5046,26 @@
       <c r="B25" s="21">
         <v>1</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="60"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="72"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="73"/>
     </row>
     <row r="28" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="57"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
     </row>
     <row r="29" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
@@ -5272,7 +5246,7 @@
   <cols>
     <col min="1" max="1" width="13.109375" style="31" customWidth="1"/>
     <col min="2" max="2" width="22" style="31" customWidth="1"/>
-    <col min="3" max="3" width="20" style="31" customWidth="1"/>
+    <col min="3" max="3" width="24" style="31" customWidth="1"/>
     <col min="4" max="4" width="22" style="31" customWidth="1"/>
     <col min="5" max="5" width="12" style="31" customWidth="1"/>
     <col min="6" max="7" width="22" style="31" customWidth="1"/>
@@ -5290,7 +5264,7 @@
     <col min="28" max="28" width="14" style="31" customWidth="1"/>
     <col min="29" max="29" width="50" style="31" customWidth="1"/>
     <col min="30" max="30" width="55" style="31" customWidth="1"/>
-    <col min="31" max="31" width="22" style="85" customWidth="1"/>
+    <col min="31" max="31" width="22" style="64" customWidth="1"/>
     <col min="32" max="16384" width="21.109375" style="31"/>
   </cols>
   <sheetData>
@@ -5344,10 +5318,10 @@
         <v>74</v>
       </c>
       <c r="Q1" s="30" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="R1" s="30" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="S1" s="30" t="s">
         <v>75</v>
@@ -5393,23 +5367,23 @@
       <c r="A2" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="88" t="s">
-        <v>145</v>
+      <c r="B2" s="67" t="s">
+        <v>144</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="32" t="s">
         <v>112</v>
-      </c>
-      <c r="D2" s="32" t="s">
-        <v>113</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H2" s="41">
         <v>1.5</v>
@@ -5421,7 +5395,7 @@
         <v>1.4</v>
       </c>
       <c r="K2" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L2" s="41">
         <v>15.077949</v>
@@ -5433,7 +5407,7 @@
         <v>14</v>
       </c>
       <c r="O2" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P2" s="34">
         <v>2024</v>
@@ -5445,13 +5419,13 @@
         <v>2040</v>
       </c>
       <c r="S2" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T2" s="35">
         <v>220123498</v>
       </c>
       <c r="U2" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V2" s="25">
         <v>57.062100000000001</v>
@@ -5460,51 +5434,51 @@
         <v>9.9770000000000003</v>
       </c>
       <c r="X2" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y2" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z2" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA2" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="Z2" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA2" s="32" t="s">
-        <v>148</v>
-      </c>
       <c r="AB2" s="50" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AC2" s="32" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="AD2" s="32" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AE2" s="55" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="B3" s="88" t="s">
-        <v>501</v>
+        <v>148</v>
+      </c>
+      <c r="B3" s="67" t="s">
+        <v>497</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H3" s="33">
         <v>0.12330000000000001</v>
@@ -5516,7 +5490,7 @@
         <v>0.112</v>
       </c>
       <c r="K3" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L3" s="42">
         <v>1.2330000000000001</v>
@@ -5528,7 +5502,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="O3" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P3" s="34">
         <v>2025</v>
@@ -5540,13 +5514,13 @@
         <v>2037</v>
       </c>
       <c r="S3" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T3" s="35">
         <v>31238542</v>
       </c>
       <c r="U3" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V3" s="25">
         <v>44.464755134852901</v>
@@ -5555,60 +5529,60 @@
         <v>12.2450955929227</v>
       </c>
       <c r="X3" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y3" s="32" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="Z3" s="32" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AA3" s="32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB3" s="50" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AC3" s="32" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="AD3" s="32" t="s">
-        <v>505</v>
-      </c>
-      <c r="AE3" s="80" t="s">
-        <v>502</v>
+        <v>501</v>
+      </c>
+      <c r="AE3" s="59" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" s="87" t="s">
-        <v>365</v>
+        <v>99</v>
+      </c>
+      <c r="B4" s="66" t="s">
+        <v>362</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I4" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J4" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K4" s="43">
         <v>2.2000000000000001E-3</v>
@@ -5617,7 +5591,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="M4" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N4" s="43">
         <v>2.1999999999999999E-2</v>
@@ -5635,13 +5609,13 @@
         <v>2036</v>
       </c>
       <c r="S4" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T4" s="39">
         <v>3168000</v>
       </c>
       <c r="U4" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V4" s="28">
         <v>43.327720234653299</v>
@@ -5650,51 +5624,51 @@
         <v>-3.1153158320413699</v>
       </c>
       <c r="X4" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y4" s="36" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="Z4" s="36" t="s">
+        <v>427</v>
+      </c>
+      <c r="AA4" s="36" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB4" s="50" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC4" s="36" t="s">
+        <v>429</v>
+      </c>
+      <c r="AD4" s="36" t="s">
         <v>430</v>
-      </c>
-      <c r="AA4" s="36" t="s">
-        <v>367</v>
-      </c>
-      <c r="AB4" s="50" t="s">
-        <v>444</v>
-      </c>
-      <c r="AC4" s="36" t="s">
-        <v>432</v>
-      </c>
-      <c r="AD4" s="36" t="s">
-        <v>433</v>
       </c>
       <c r="AE4" s="54" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="B5" s="88" t="s">
-        <v>447</v>
+        <v>126</v>
+      </c>
+      <c r="B5" s="67" t="s">
+        <v>444</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H5" s="33">
         <v>1</v>
@@ -5706,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L5" s="42">
         <v>10</v>
@@ -5718,10 +5692,10 @@
         <v>10</v>
       </c>
       <c r="O5" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P5" s="34" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="Q5" s="34">
         <v>2030</v>
@@ -5730,13 +5704,13 @@
         <v>2040</v>
       </c>
       <c r="S5" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T5" s="35">
         <v>170000000</v>
       </c>
       <c r="U5" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V5" s="25">
         <v>46.809800000000003</v>
@@ -5745,75 +5719,75 @@
         <v>-0.13900000000000001</v>
       </c>
       <c r="X5" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y5" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z5" s="32" t="s">
+        <v>448</v>
+      </c>
+      <c r="AA5" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="Z5" s="32" t="s">
-        <v>451</v>
-      </c>
-      <c r="AA5" s="32" t="s">
-        <v>203</v>
-      </c>
       <c r="AB5" s="50" t="s">
+        <v>447</v>
+      </c>
+      <c r="AC5" s="32" t="s">
+        <v>449</v>
+      </c>
+      <c r="AD5" s="32" t="s">
         <v>450</v>
       </c>
-      <c r="AC5" s="32" t="s">
-        <v>452</v>
-      </c>
-      <c r="AD5" s="32" t="s">
-        <v>453</v>
-      </c>
-      <c r="AE5" s="81" t="s">
+      <c r="AE5" s="60" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="B6" s="88" t="s">
-        <v>355</v>
+        <v>148</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>352</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H6" s="33">
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="I6" s="37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J6" s="37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L6" s="42">
         <v>0.128</v>
       </c>
       <c r="M6" s="37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N6" s="37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O6" s="37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P6" s="34">
         <v>2025</v>
@@ -5825,66 +5799,66 @@
         <v>2038</v>
       </c>
       <c r="S6" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T6" s="35">
         <v>7958244</v>
       </c>
       <c r="U6" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="V6" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="W6" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="X6" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y6" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z6" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="AA6" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="AB6" s="50" t="s">
+        <v>456</v>
+      </c>
+      <c r="AC6" s="32" t="s">
         <v>454</v>
       </c>
-      <c r="V6" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="W6" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="X6" s="23" t="s">
-        <v>302</v>
-      </c>
-      <c r="Y6" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z6" s="32" t="s">
-        <v>357</v>
-      </c>
-      <c r="AA6" s="32" t="s">
-        <v>358</v>
-      </c>
-      <c r="AB6" s="50" t="s">
-        <v>459</v>
-      </c>
-      <c r="AC6" s="32" t="s">
-        <v>457</v>
-      </c>
       <c r="AD6" s="32" t="s">
-        <v>458</v>
-      </c>
-      <c r="AE6" s="80" t="s">
+        <v>455</v>
+      </c>
+      <c r="AE6" s="59" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="88" t="s">
-        <v>138</v>
+      <c r="B7" s="67" t="s">
+        <v>137</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="32" t="s">
         <v>112</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>448</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H7" s="33">
         <v>0.8</v>
@@ -5896,7 +5870,7 @@
         <v>0.8</v>
       </c>
       <c r="K7" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L7" s="42">
         <v>7.8</v>
@@ -5908,7 +5882,7 @@
         <v>8</v>
       </c>
       <c r="O7" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P7" s="34">
         <v>2023</v>
@@ -5920,13 +5894,13 @@
         <v>2038</v>
       </c>
       <c r="S7" s="23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T7" s="35">
         <v>189694949</v>
       </c>
       <c r="U7" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V7" s="25">
         <v>43.232830995956597</v>
@@ -5935,51 +5909,51 @@
         <v>27.594387234972402</v>
       </c>
       <c r="X7" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y7" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z7" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA7" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="Y7" s="32" t="s">
-        <v>425</v>
-      </c>
-      <c r="Z7" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA7" s="32" t="s">
-        <v>141</v>
-      </c>
       <c r="AB7" s="50" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AC7" s="32" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AD7" s="32" t="s">
-        <v>462</v>
-      </c>
-      <c r="AE7" s="81" t="s">
+        <v>459</v>
+      </c>
+      <c r="AE7" s="60" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="88" t="s">
-        <v>128</v>
-      </c>
       <c r="C8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="32" t="s">
         <v>112</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>113</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H8" s="33">
         <v>0.8</v>
@@ -5991,7 +5965,7 @@
         <v>0.8</v>
       </c>
       <c r="K8" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L8" s="42">
         <v>8</v>
@@ -6003,10 +5977,10 @@
         <v>8</v>
       </c>
       <c r="O8" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="Q8" s="34">
         <v>2029</v>
@@ -6015,13 +5989,13 @@
         <v>2039</v>
       </c>
       <c r="S8" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T8" s="35" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="U8" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V8" s="25">
         <v>50.575420999999999</v>
@@ -6030,75 +6004,75 @@
         <v>3.4423240000000002</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y8" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z8" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA8" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="Z8" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA8" s="32" t="s">
+      <c r="AB8" s="50" t="s">
+        <v>461</v>
+      </c>
+      <c r="AC8" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="AB8" s="50" t="s">
-        <v>464</v>
-      </c>
-      <c r="AC8" s="32" t="s">
-        <v>133</v>
-      </c>
       <c r="AD8" s="32" t="s">
-        <v>465</v>
-      </c>
-      <c r="AE8" s="81" t="s">
+        <v>462</v>
+      </c>
+      <c r="AE8" s="60" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="B9" s="87" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="66" t="s">
+        <v>265</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="D9" s="36" t="s">
         <v>267</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>269</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>50</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I9" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J9" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K9" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L9" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M9" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N9" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O9" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P9" s="38">
         <v>2025</v>
@@ -6110,13 +6084,13 @@
         <v>2040</v>
       </c>
       <c r="S9" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T9" s="39">
         <v>169300000</v>
       </c>
       <c r="U9" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V9" s="28">
         <v>37.981699999999996</v>
@@ -6125,27 +6099,27 @@
         <v>23.365600000000001</v>
       </c>
       <c r="X9" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y9" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="Z9" s="36" t="s">
+        <v>269</v>
+      </c>
+      <c r="AA9" s="36" t="s">
         <v>270</v>
       </c>
-      <c r="Z9" s="36" t="s">
+      <c r="AB9" s="50" t="s">
+        <v>465</v>
+      </c>
+      <c r="AC9" s="36" t="s">
+        <v>464</v>
+      </c>
+      <c r="AD9" s="36" t="s">
         <v>271</v>
       </c>
-      <c r="AA9" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="AB9" s="50" t="s">
-        <v>468</v>
-      </c>
-      <c r="AC9" s="36" t="s">
-        <v>467</v>
-      </c>
-      <c r="AD9" s="36" t="s">
-        <v>273</v>
-      </c>
-      <c r="AE9" s="81" t="s">
+      <c r="AE9" s="60" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6153,26 +6127,26 @@
       <c r="A10" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="88" t="s">
-        <v>470</v>
+      <c r="B10" s="67" t="s">
+        <v>467</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H10" s="33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I10" s="42">
         <v>0.78300000000000003</v>
@@ -6181,7 +6155,7 @@
         <v>0.78300000000000003</v>
       </c>
       <c r="K10" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L10" s="42">
         <v>7.83</v>
@@ -6193,7 +6167,7 @@
         <v>7.83</v>
       </c>
       <c r="O10" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P10" s="34">
         <v>2021</v>
@@ -6205,7 +6179,7 @@
         <v>2038</v>
       </c>
       <c r="S10" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T10" s="35">
         <v>180000000</v>
@@ -6220,75 +6194,75 @@
         <v>18.103999999999999</v>
       </c>
       <c r="X10" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y10" s="32" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="Z10" s="32" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AA10" s="32" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AB10" s="50" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="AC10" s="32" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AD10" s="32" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AE10" s="54" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="B11" s="88" t="s">
-        <v>338</v>
+        <v>133</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>335</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="I11" s="79">
+        <v>92</v>
+      </c>
+      <c r="I11" s="58">
         <v>7.6649999999999999E-3</v>
       </c>
-      <c r="J11" s="79" t="s">
-        <v>93</v>
+      <c r="J11" s="58" t="s">
+        <v>92</v>
       </c>
       <c r="K11" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L11" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M11" s="42">
         <v>0.08</v>
       </c>
       <c r="N11" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O11" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P11" s="34">
         <v>2025</v>
@@ -6300,13 +6274,13 @@
         <v>2037</v>
       </c>
       <c r="S11" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T11" s="35" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="U11" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V11" s="25">
         <v>59.592303479664103</v>
@@ -6315,27 +6289,27 @@
         <v>5.8029778441568904</v>
       </c>
       <c r="X11" s="23" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Y11" s="32" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="Z11" s="32" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AA11" s="32" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AB11" s="50" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="AC11" s="32" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="AD11" s="32" t="s">
-        <v>541</v>
-      </c>
-      <c r="AE11" s="81" t="s">
+        <v>537</v>
+      </c>
+      <c r="AE11" s="60" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6343,23 +6317,23 @@
       <c r="A12" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="87" t="s">
-        <v>228</v>
+      <c r="B12" s="66" t="s">
+        <v>227</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H12" s="37">
         <v>1.3</v>
@@ -6368,7 +6342,7 @@
         <v>1.2</v>
       </c>
       <c r="J12" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K12" s="43">
         <v>1.2</v>
@@ -6380,7 +6354,7 @@
         <v>12</v>
       </c>
       <c r="N12" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O12" s="43">
         <v>12</v>
@@ -6395,7 +6369,7 @@
         <v>2038</v>
       </c>
       <c r="S12" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T12" s="39">
         <v>109816528</v>
@@ -6410,27 +6384,27 @@
         <v>9.5841999999999992</v>
       </c>
       <c r="X12" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y12" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="Z12" s="36" t="s">
+        <v>448</v>
+      </c>
+      <c r="AA12" s="36" t="s">
         <v>230</v>
       </c>
-      <c r="Z12" s="36" t="s">
-        <v>451</v>
-      </c>
-      <c r="AA12" s="36" t="s">
-        <v>231</v>
-      </c>
       <c r="AB12" s="50" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="AC12" s="36" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="AD12" s="36" t="s">
-        <v>543</v>
-      </c>
-      <c r="AE12" s="80" t="s">
+        <v>539</v>
+      </c>
+      <c r="AE12" s="59" t="s">
         <v>23</v>
       </c>
     </row>
@@ -6438,23 +6412,23 @@
       <c r="A13" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="87" t="s">
-        <v>188</v>
+      <c r="B13" s="66" t="s">
+        <v>187</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>42</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H13" s="43">
         <v>0.57999999999999996</v>
@@ -6466,7 +6440,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="K13" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L13" s="43">
         <v>5.8</v>
@@ -6478,7 +6452,7 @@
         <v>5.8</v>
       </c>
       <c r="O13" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P13" s="38">
         <v>2023</v>
@@ -6490,7 +6464,7 @@
         <v>2038</v>
       </c>
       <c r="S13" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T13" s="39">
         <v>125198197</v>
@@ -6505,51 +6479,51 @@
         <v>1.78234746701462</v>
       </c>
       <c r="X13" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y13" s="36" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="Z13" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="AA13" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="AA13" s="36" t="s">
+      <c r="AB13" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="AB13" s="29" t="s">
-        <v>192</v>
-      </c>
       <c r="AC13" s="36" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AD13" s="36" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="AE13" s="55" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="B14" s="87" t="s">
-        <v>305</v>
+        <v>148</v>
+      </c>
+      <c r="B14" s="66" t="s">
+        <v>302</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>56</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H14" s="37">
         <v>6.4000000000000001E-2</v>
@@ -6561,7 +6535,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="K14" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L14" s="43">
         <v>0.64</v>
@@ -6573,7 +6547,7 @@
         <v>0.64</v>
       </c>
       <c r="O14" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P14" s="38">
         <v>2025</v>
@@ -6585,13 +6559,13 @@
         <v>2038</v>
       </c>
       <c r="S14" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T14" s="39">
         <v>23635998</v>
       </c>
       <c r="U14" s="39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V14" s="28">
         <v>44.826999999999998</v>
@@ -6600,27 +6574,27 @@
         <v>11.614000000000001</v>
       </c>
       <c r="X14" s="22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y14" s="36" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Z14" s="36" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AA14" s="36" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="AB14" s="50" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="AC14" s="36" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="AD14" s="36" t="s">
-        <v>528</v>
-      </c>
-      <c r="AE14" s="80" t="s">
+        <v>524</v>
+      </c>
+      <c r="AE14" s="59" t="s">
         <v>23</v>
       </c>
     </row>
@@ -6628,23 +6602,23 @@
       <c r="A15" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="87" t="s">
-        <v>198</v>
+      <c r="B15" s="66" t="s">
+        <v>197</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="36" t="s">
         <v>112</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>113</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>42</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="H15" s="37">
         <v>0.7</v>
@@ -6656,7 +6630,7 @@
         <v>0.7</v>
       </c>
       <c r="K15" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L15" s="43">
         <v>7</v>
@@ -6668,7 +6642,7 @@
         <v>7</v>
       </c>
       <c r="O15" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P15" s="38">
         <v>2024</v>
@@ -6680,13 +6654,13 @@
         <v>2041</v>
       </c>
       <c r="S15" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T15" s="39">
         <v>119682059</v>
       </c>
       <c r="U15" s="39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V15" s="28">
         <v>43.186100000000003</v>
@@ -6695,52 +6669,52 @@
         <v>0.99039999999999995</v>
       </c>
       <c r="X15" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y15" s="36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Z15" s="36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AA15" s="36"/>
       <c r="AB15" s="50" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AC15" s="36" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="AD15" s="36" t="s">
-        <v>531</v>
-      </c>
-      <c r="AE15" s="80" t="s">
+        <v>527</v>
+      </c>
+      <c r="AE15" s="59" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="B16" s="88" t="s">
-        <v>364</v>
+        <v>126</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>361</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>59</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H16" s="33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I16" s="42">
         <v>1.2</v>
@@ -6749,10 +6723,10 @@
         <v>1.2</v>
       </c>
       <c r="K16" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L16" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M16" s="42">
         <v>12</v>
@@ -6761,7 +6735,7 @@
         <v>12</v>
       </c>
       <c r="O16" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P16" s="34">
         <v>2025</v>
@@ -6773,13 +6747,13 @@
         <v>2042</v>
       </c>
       <c r="S16" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T16" s="35" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="U16" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V16" s="25">
         <v>45.290985428950698</v>
@@ -6788,65 +6762,65 @@
         <v>25.1109549184484</v>
       </c>
       <c r="X16" s="23" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Y16" s="32" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="Z16" s="32" t="s">
+        <v>542</v>
+      </c>
+      <c r="AA16" s="32" t="s">
+        <v>361</v>
+      </c>
+      <c r="AB16" s="50" t="s">
+        <v>543</v>
+      </c>
+      <c r="AC16" s="32" t="s">
         <v>546</v>
       </c>
-      <c r="AA16" s="32" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB16" s="50" t="s">
+      <c r="AD16" s="32" t="s">
         <v>547</v>
       </c>
-      <c r="AC16" s="32" t="s">
-        <v>550</v>
-      </c>
-      <c r="AD16" s="32" t="s">
-        <v>551</v>
-      </c>
-      <c r="AE16" s="81" t="s">
-        <v>552</v>
+      <c r="AE16" s="60" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="88" t="s">
-        <v>315</v>
+        <v>99</v>
+      </c>
+      <c r="B17" s="67" t="s">
+        <v>312</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="H17" s="78">
+        <v>550</v>
+      </c>
+      <c r="H17" s="57">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="I17" s="78">
+      <c r="I17" s="57">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="J17" s="78">
+      <c r="J17" s="57">
         <v>4.5999999999999999E-3</v>
       </c>
       <c r="K17" s="42" t="s">
-        <v>93</v>
-      </c>
-      <c r="L17" s="79">
+        <v>92</v>
+      </c>
+      <c r="L17" s="58">
         <v>4.5689E-2</v>
       </c>
       <c r="M17" s="42">
@@ -6856,7 +6830,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="O17" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P17" s="34">
         <v>2024</v>
@@ -6868,13 +6842,13 @@
         <v>2031</v>
       </c>
       <c r="S17" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T17" s="35">
         <v>30497000</v>
       </c>
       <c r="U17" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V17" s="23">
         <v>51.870851200822599</v>
@@ -6883,51 +6857,51 @@
         <v>4.30094696894741</v>
       </c>
       <c r="X17" s="23" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Y17" s="32" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="Z17" s="32" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AA17" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AB17" s="26" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AC17" s="32" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="AD17" s="32" t="s">
-        <v>557</v>
-      </c>
-      <c r="AE17" s="82" t="s">
-        <v>555</v>
+        <v>553</v>
+      </c>
+      <c r="AE17" s="61" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="88" t="s">
-        <v>240</v>
+      <c r="B18" s="67" t="s">
+        <v>239</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="32" t="s">
         <v>112</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>113</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H18" s="42">
         <v>1.3</v>
@@ -6939,7 +6913,7 @@
         <v>1.3</v>
       </c>
       <c r="K18" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L18" s="42">
         <v>12.56</v>
@@ -6951,7 +6925,7 @@
         <v>13</v>
       </c>
       <c r="O18" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P18" s="34">
         <v>2025</v>
@@ -6963,13 +6937,13 @@
         <v>2040</v>
       </c>
       <c r="S18" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T18" s="35">
         <v>157000000</v>
       </c>
       <c r="U18" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V18" s="25">
         <v>52.489100000000001</v>
@@ -6978,51 +6952,51 @@
         <v>13.836399999999999</v>
       </c>
       <c r="X18" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y18" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z18" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA18" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="Z18" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA18" s="32" t="s">
+      <c r="AB18" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="AB18" s="26" t="s">
-        <v>244</v>
-      </c>
       <c r="AC18" s="32" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AD18" s="32" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="AE18" s="55" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="19" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="87" t="s">
+      <c r="C19" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="D19" s="36" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F19" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="H19" s="37">
         <v>0.02</v>
@@ -7031,7 +7005,7 @@
         <v>0.02</v>
       </c>
       <c r="J19" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K19" s="43">
         <v>0.02</v>
@@ -7043,7 +7017,7 @@
         <v>0.2</v>
       </c>
       <c r="N19" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O19" s="43">
         <v>0.2</v>
@@ -7058,13 +7032,13 @@
         <v>2036</v>
       </c>
       <c r="S19" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T19" s="39">
         <v>4265136</v>
       </c>
       <c r="U19" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V19" s="28">
         <v>50.569000000000003</v>
@@ -7073,75 +7047,75 @@
         <v>5.359</v>
       </c>
       <c r="X19" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y19" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z19" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="Z19" s="36" t="s">
+      <c r="AA19" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="AA19" s="36" t="s">
+      <c r="AB19" s="50" t="s">
+        <v>557</v>
+      </c>
+      <c r="AC19" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD19" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="AB19" s="50" t="s">
-        <v>561</v>
-      </c>
-      <c r="AC19" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="AD19" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="AE19" s="82" t="s">
-        <v>560</v>
+      <c r="AE19" s="61" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="20" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B20" s="87" t="s">
-        <v>294</v>
+      <c r="B20" s="66" t="s">
+        <v>291</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>49</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="H20" s="37">
         <v>2.11</v>
       </c>
       <c r="I20" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J20" s="43">
         <v>2.11</v>
       </c>
       <c r="K20" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L20" s="43">
         <v>21.1</v>
       </c>
       <c r="M20" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N20" s="43">
         <v>21.1</v>
       </c>
       <c r="O20" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P20" s="38">
         <v>2023</v>
@@ -7153,7 +7127,7 @@
         <v>2037</v>
       </c>
       <c r="S20" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T20" s="39">
         <v>115000000</v>
@@ -7168,93 +7142,93 @@
         <v>-22.0167</v>
       </c>
       <c r="X20" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y20" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z20" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="AA20" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="AB20" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="Z20" s="36" t="s">
-        <v>296</v>
-      </c>
-      <c r="AA20" s="36" t="s">
-        <v>297</v>
-      </c>
-      <c r="AB20" s="29" t="s">
-        <v>298</v>
-      </c>
       <c r="AC20" s="36" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="AD20" s="36" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="AE20" s="54" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="21" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="B21" s="87" t="s">
-        <v>387</v>
+        <v>133</v>
+      </c>
+      <c r="B21" s="66" t="s">
+        <v>384</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>268</v>
+        <v>463</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="H21" s="86">
+        <v>210</v>
+      </c>
+      <c r="H21" s="65">
         <v>0.63600000000000001</v>
       </c>
       <c r="I21" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J21" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K21" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L21" s="52">
         <v>6.3620479999999997</v>
       </c>
       <c r="M21" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N21" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O21" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P21" s="38">
         <v>2025</v>
       </c>
       <c r="Q21" s="38" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="R21" s="38" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="S21" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T21" s="39">
         <v>25400000</v>
       </c>
       <c r="U21" s="39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V21" s="28">
         <v>41.352637812781921</v>
@@ -7263,60 +7237,60 @@
         <v>2.1794021596499702</v>
       </c>
       <c r="X21" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y21" s="32" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="Z21" s="36" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="AA21" s="36" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AB21" s="50" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="AC21" s="36" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="AD21" s="36" t="s">
-        <v>390</v>
-      </c>
-      <c r="AE21" s="81" t="s">
-        <v>552</v>
+        <v>387</v>
+      </c>
+      <c r="AE21" s="60" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="22" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="B22" s="88" t="s">
-        <v>299</v>
+        <v>99</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>296</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="H22" s="79">
+        <v>298</v>
+      </c>
+      <c r="H22" s="58">
         <v>1.7904E-2</v>
       </c>
       <c r="I22" s="42">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="J22" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K22" s="42">
         <v>1.2999999999999999E-2</v>
@@ -7328,7 +7302,7 @@
         <v>0.13</v>
       </c>
       <c r="N22" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O22" s="42">
         <v>0.13</v>
@@ -7343,7 +7317,7 @@
         <v>2039</v>
       </c>
       <c r="S22" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T22" s="35">
         <v>4150000</v>
@@ -7358,51 +7332,51 @@
         <v>13.253440646806</v>
       </c>
       <c r="X22" s="23" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Y22" s="31" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="Z22" s="32" t="s">
+        <v>565</v>
+      </c>
+      <c r="AA22" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="AB22" s="50" t="s">
+        <v>566</v>
+      </c>
+      <c r="AC22" s="32" t="s">
+        <v>567</v>
+      </c>
+      <c r="AD22" s="32" t="s">
+        <v>568</v>
+      </c>
+      <c r="AE22" s="55" t="s">
         <v>569</v>
-      </c>
-      <c r="AA22" s="32" t="s">
-        <v>304</v>
-      </c>
-      <c r="AB22" s="50" t="s">
-        <v>570</v>
-      </c>
-      <c r="AC22" s="32" t="s">
-        <v>571</v>
-      </c>
-      <c r="AD22" s="32" t="s">
-        <v>572</v>
-      </c>
-      <c r="AE22" s="55" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="23" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="B23" s="87" t="s">
-        <v>281</v>
+        <v>148</v>
+      </c>
+      <c r="B23" s="66" t="s">
+        <v>279</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>282</v>
+        <v>651</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>57</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="H23" s="37">
         <v>0.56499999999999995</v>
@@ -7414,7 +7388,7 @@
         <v>0.5</v>
       </c>
       <c r="K23" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L23" s="43">
         <v>5.65</v>
@@ -7426,7 +7400,7 @@
         <v>5</v>
       </c>
       <c r="O23" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P23" s="38">
         <v>2025</v>
@@ -7438,7 +7412,7 @@
         <v>2037</v>
       </c>
       <c r="S23" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T23" s="39">
         <v>48445901</v>
@@ -7453,51 +7427,51 @@
         <v>18.9154603437044</v>
       </c>
       <c r="X23" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y23" s="36" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="Z23" s="36" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AA23" s="36" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AB23" s="50" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="AC23" s="36" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="AD23" s="36" t="s">
-        <v>580</v>
-      </c>
-      <c r="AE23" s="80" t="s">
-        <v>578</v>
+        <v>576</v>
+      </c>
+      <c r="AE23" s="59" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="24" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="B24" s="87" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="66" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D24" s="36" t="s">
         <v>204</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="D24" s="36" t="s">
-        <v>205</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>42</v>
       </c>
       <c r="F24" s="45" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G24" s="45" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="H24" s="37">
         <v>0.2</v>
@@ -7506,7 +7480,7 @@
         <v>0.35</v>
       </c>
       <c r="J24" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K24" s="43">
         <v>0.35</v>
@@ -7518,7 +7492,7 @@
         <v>3.5</v>
       </c>
       <c r="N24" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O24" s="43">
         <v>3.5</v>
@@ -7533,7 +7507,7 @@
         <v>2040</v>
       </c>
       <c r="S24" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T24" s="39">
         <v>40000000</v>
@@ -7548,51 +7522,51 @@
         <v>1.1835034670687401</v>
       </c>
       <c r="X24" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="Y24" s="36" t="s">
+        <v>590</v>
+      </c>
+      <c r="Z24" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="Y24" s="36" t="s">
-        <v>594</v>
-      </c>
-      <c r="Z24" s="36" t="s">
+      <c r="AA24" s="36" t="s">
         <v>207</v>
       </c>
-      <c r="AA24" s="36" t="s">
-        <v>208</v>
-      </c>
       <c r="AB24" s="50" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="AC24" s="36" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="AD24" s="36" t="s">
-        <v>593</v>
-      </c>
-      <c r="AE24" s="81" t="s">
-        <v>552</v>
+        <v>589</v>
+      </c>
+      <c r="AE24" s="60" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="25" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="B25" s="87" t="s">
-        <v>313</v>
+        <v>126</v>
+      </c>
+      <c r="B25" s="66" t="s">
+        <v>310</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="36" t="s">
         <v>112</v>
-      </c>
-      <c r="D25" s="36" t="s">
-        <v>113</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>56</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="H25" s="37">
         <v>1</v>
@@ -7604,7 +7578,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L25" s="43">
         <v>10</v>
@@ -7616,7 +7590,7 @@
         <v>10</v>
       </c>
       <c r="O25" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P25" s="38">
         <v>2024</v>
@@ -7628,13 +7602,13 @@
         <v>2040</v>
       </c>
       <c r="S25" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T25" s="39">
         <v>216000000</v>
       </c>
       <c r="U25" s="39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V25" s="28">
         <v>45.686354081466597</v>
@@ -7643,75 +7617,75 @@
         <v>9.4679295616956907</v>
       </c>
       <c r="X25" s="22" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Y25" s="36" t="s">
+        <v>579</v>
+      </c>
+      <c r="Z25" s="36" t="s">
+        <v>580</v>
+      </c>
+      <c r="AA25" s="36" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB25" s="50" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC25" s="36" t="s">
+        <v>582</v>
+      </c>
+      <c r="AD25" s="36" t="s">
         <v>583</v>
       </c>
-      <c r="Z25" s="36" t="s">
-        <v>584</v>
-      </c>
-      <c r="AA25" s="36" t="s">
-        <v>314</v>
-      </c>
-      <c r="AB25" s="50" t="s">
-        <v>585</v>
-      </c>
-      <c r="AC25" s="36" t="s">
-        <v>586</v>
-      </c>
-      <c r="AD25" s="36" t="s">
-        <v>587</v>
-      </c>
-      <c r="AE25" s="81" t="s">
-        <v>552</v>
+      <c r="AE25" s="60" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="26" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="87" t="s">
-        <v>324</v>
+      <c r="B26" s="66" t="s">
+        <v>321</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H26" s="86">
+        <v>93</v>
+      </c>
+      <c r="H26" s="65">
         <v>2.2800000000000001E-2</v>
       </c>
       <c r="I26" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J26" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K26" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L26" s="43">
         <v>0.228163</v>
       </c>
       <c r="M26" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N26" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O26" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P26" s="38">
         <v>2024</v>
@@ -7723,13 +7697,13 @@
         <v>2033</v>
       </c>
       <c r="S26" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T26" s="39">
         <v>40000000</v>
       </c>
       <c r="U26" s="39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V26" s="22">
         <v>59.121267699503399</v>
@@ -7738,51 +7712,51 @@
         <v>9.6300609243118291</v>
       </c>
       <c r="X26" s="22" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Y26" s="36" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="Z26" s="36" t="s">
+        <v>323</v>
+      </c>
+      <c r="AA26" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="AB26" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="AC26" s="36" t="s">
         <v>326</v>
       </c>
-      <c r="AA26" s="36" t="s">
+      <c r="AD26" s="36" t="s">
         <v>327</v>
       </c>
-      <c r="AB26" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="AC26" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="AD26" s="36" t="s">
-        <v>330</v>
-      </c>
       <c r="AE26" s="55" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="27" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="88" t="s">
-        <v>193</v>
+      <c r="B27" s="67" t="s">
+        <v>192</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="H27" s="33">
         <v>0.23252429999999999</v>
@@ -7791,7 +7765,7 @@
         <v>0.19500000000000001</v>
       </c>
       <c r="J27" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K27" s="42">
         <v>0.19500000000000001</v>
@@ -7803,7 +7777,7 @@
         <v>1.95</v>
       </c>
       <c r="N27" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O27" s="42">
         <v>1.95</v>
@@ -7818,7 +7792,7 @@
         <v>2038</v>
       </c>
       <c r="S27" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T27" s="35">
         <v>115190750</v>
@@ -7833,51 +7807,51 @@
         <v>4.6899272399638701</v>
       </c>
       <c r="X27" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y27" s="32" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="Z27" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="AA27" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="AA27" s="32" t="s">
+      <c r="AB27" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="AB27" s="26" t="s">
-        <v>197</v>
-      </c>
       <c r="AC27" s="32" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AD27" s="32" t="s">
-        <v>598</v>
-      </c>
-      <c r="AE27" s="80" t="s">
-        <v>599</v>
+        <v>594</v>
+      </c>
+      <c r="AE27" s="59" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="B28" s="88" t="s">
-        <v>155</v>
+        <v>126</v>
+      </c>
+      <c r="B28" s="67" t="s">
+        <v>154</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D28" s="32" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H28" s="33">
         <v>0.26</v>
@@ -7886,7 +7860,7 @@
         <v>0.25</v>
       </c>
       <c r="J28" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K28" s="42">
         <v>0.25</v>
@@ -7898,7 +7872,7 @@
         <v>2.5</v>
       </c>
       <c r="N28" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O28" s="42">
         <v>2.5</v>
@@ -7913,7 +7887,7 @@
         <v>2038</v>
       </c>
       <c r="S28" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T28" s="35">
         <v>40000000</v>
@@ -7928,51 +7902,51 @@
         <v>11.8749856575691</v>
       </c>
       <c r="X28" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y28" s="32" t="s">
+        <v>598</v>
+      </c>
+      <c r="Z28" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="AA28" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="AB28" s="50" t="s">
+        <v>599</v>
+      </c>
+      <c r="AC28" s="32" t="s">
+        <v>600</v>
+      </c>
+      <c r="AD28" s="32" t="s">
+        <v>601</v>
+      </c>
+      <c r="AE28" s="60" t="s">
         <v>602</v>
-      </c>
-      <c r="Z28" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="AA28" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB28" s="50" t="s">
-        <v>603</v>
-      </c>
-      <c r="AC28" s="32" t="s">
-        <v>604</v>
-      </c>
-      <c r="AD28" s="32" t="s">
-        <v>605</v>
-      </c>
-      <c r="AE28" s="81" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B29" s="88" t="s">
-        <v>232</v>
+      <c r="B29" s="67" t="s">
+        <v>231</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H29" s="42">
         <v>1.5</v>
@@ -7984,7 +7958,7 @@
         <v>1.5</v>
       </c>
       <c r="K29" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L29" s="42">
         <v>15</v>
@@ -7996,7 +7970,7 @@
         <v>15</v>
       </c>
       <c r="O29" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P29" s="34">
         <v>2024</v>
@@ -8008,13 +7982,13 @@
         <v>2041</v>
       </c>
       <c r="S29" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T29" s="35">
         <v>228721666</v>
       </c>
       <c r="U29" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V29" s="25">
         <v>51.297800000000002</v>
@@ -8023,51 +7997,51 @@
         <v>7.0148000000000001</v>
       </c>
       <c r="X29" s="23" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y29" s="32" t="s">
+        <v>603</v>
+      </c>
+      <c r="Z29" s="32" t="s">
+        <v>604</v>
+      </c>
+      <c r="AA29" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB29" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="AC29" s="32" t="s">
+        <v>605</v>
+      </c>
+      <c r="AD29" s="32" t="s">
+        <v>606</v>
+      </c>
+      <c r="AE29" s="59" t="s">
         <v>607</v>
-      </c>
-      <c r="Z29" s="32" t="s">
-        <v>608</v>
-      </c>
-      <c r="AA29" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="AB29" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="AC29" s="32" t="s">
-        <v>609</v>
-      </c>
-      <c r="AD29" s="32" t="s">
-        <v>610</v>
-      </c>
-      <c r="AE29" s="80" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B30" s="87" t="s">
-        <v>236</v>
+      <c r="B30" s="66" t="s">
+        <v>235</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="36" t="s">
         <v>112</v>
-      </c>
-      <c r="D30" s="36" t="s">
-        <v>113</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H30" s="37">
         <v>0.7</v>
@@ -8079,7 +8053,7 @@
         <v>0.7</v>
       </c>
       <c r="K30" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L30" s="43">
         <v>7.27</v>
@@ -8091,7 +8065,7 @@
         <v>7</v>
       </c>
       <c r="O30" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P30" s="38">
         <v>2024</v>
@@ -8103,13 +8077,13 @@
         <v>2040</v>
       </c>
       <c r="S30" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T30" s="39">
         <v>191000000</v>
       </c>
       <c r="U30" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V30" s="28">
         <v>51.618000000000002</v>
@@ -8118,51 +8092,51 @@
         <v>8.5100999999999996</v>
       </c>
       <c r="X30" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y30" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="Z30" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA30" s="36" t="s">
         <v>237</v>
       </c>
-      <c r="Z30" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA30" s="36" t="s">
+      <c r="AB30" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="AB30" s="29" t="s">
-        <v>239</v>
-      </c>
       <c r="AC30" s="36" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="AD30" s="36" t="s">
-        <v>525</v>
-      </c>
-      <c r="AE30" s="80" t="s">
-        <v>523</v>
+        <v>521</v>
+      </c>
+      <c r="AE30" s="59" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B31" s="87" t="s">
-        <v>351</v>
+      <c r="B31" s="66" t="s">
+        <v>348</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="36" t="s">
         <v>112</v>
-      </c>
-      <c r="D31" s="36" t="s">
-        <v>113</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>45</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="H31" s="37">
         <v>1</v>
@@ -8174,7 +8148,7 @@
         <v>1.2</v>
       </c>
       <c r="K31" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L31" s="43">
         <v>10</v>
@@ -8186,7 +8160,7 @@
         <v>12</v>
       </c>
       <c r="O31" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P31" s="38">
         <v>2022</v>
@@ -8198,7 +8172,7 @@
         <v>2037</v>
       </c>
       <c r="S31" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T31" s="39">
         <v>228210004</v>
@@ -8213,51 +8187,51 @@
         <v>17.989599999999999</v>
       </c>
       <c r="X31" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y31" s="36" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="Z31" s="36" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AA31" s="36" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AB31" s="50" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="AC31" s="36" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="AD31" s="36" t="s">
-        <v>354</v>
-      </c>
-      <c r="AE31" s="80" t="s">
-        <v>614</v>
+        <v>351</v>
+      </c>
+      <c r="AE31" s="59" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="88" t="s">
+      <c r="B32" s="67" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="32" t="s">
         <v>112</v>
-      </c>
-      <c r="D32" s="32" t="s">
-        <v>113</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H32" s="41">
         <v>1.0045932</v>
@@ -8269,7 +8243,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="K32" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L32" s="33">
         <v>10.045932000000001</v>
@@ -8281,7 +8255,7 @@
         <v>11</v>
       </c>
       <c r="O32" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P32" s="34">
         <v>2023</v>
@@ -8293,7 +8267,7 @@
         <v>2038</v>
       </c>
       <c r="S32" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T32" s="35">
         <v>230000000</v>
@@ -8308,27 +8282,27 @@
         <v>3.9928129999999999</v>
       </c>
       <c r="X32" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y32" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z32" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="Z32" s="32" t="s">
+      <c r="AA32" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="AA32" s="32" t="s">
-        <v>118</v>
-      </c>
       <c r="AB32" s="50" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AC32" s="32" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="AD32" s="32" t="s">
-        <v>616</v>
-      </c>
-      <c r="AE32" s="83" t="s">
+        <v>612</v>
+      </c>
+      <c r="AE32" s="62" t="s">
         <v>37</v>
       </c>
     </row>
@@ -8336,20 +8310,20 @@
       <c r="A33" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="88" t="s">
-        <v>368</v>
+      <c r="B33" s="67" t="s">
+        <v>365</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="33">
@@ -8359,7 +8333,7 @@
         <v>0.15</v>
       </c>
       <c r="J33" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K33" s="42">
         <v>0.15</v>
@@ -8371,7 +8345,7 @@
         <v>1.5</v>
       </c>
       <c r="N33" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O33" s="42">
         <v>1.5</v>
@@ -8386,13 +8360,13 @@
         <v>2038</v>
       </c>
       <c r="S33" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T33" s="35">
         <v>122900000</v>
       </c>
       <c r="U33" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V33" s="23">
         <v>43.151000000000003</v>
@@ -8401,27 +8375,27 @@
         <v>-7.6859999999999999</v>
       </c>
       <c r="X33" s="23" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Y33" s="32" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="Z33" s="32" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="AA33" s="32" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="AB33" s="50" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AC33" s="32" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="AD33" s="32" t="s">
-        <v>620</v>
-      </c>
-      <c r="AE33" s="80" t="s">
+        <v>616</v>
+      </c>
+      <c r="AE33" s="59" t="s">
         <v>23</v>
       </c>
     </row>
@@ -8429,35 +8403,35 @@
       <c r="A34" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B34" s="87" t="s">
-        <v>150</v>
-      </c>
-      <c r="C34" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34" s="32" t="s">
-        <v>90</v>
+      <c r="B34" s="66" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>463</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>54</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H34" s="37">
         <v>0.28144999999999998</v>
       </c>
       <c r="I34" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J34" s="43">
         <v>0.4</v>
       </c>
       <c r="K34" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L34" s="52">
         <v>2.8</v>
@@ -8469,7 +8443,7 @@
         <v>4</v>
       </c>
       <c r="O34" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P34" s="38">
         <v>2024</v>
@@ -8481,7 +8455,7 @@
         <v>2034</v>
       </c>
       <c r="S34" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T34" s="39">
         <v>41041661</v>
@@ -8496,75 +8470,75 @@
         <v>8.4393999999999991</v>
       </c>
       <c r="X34" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y34" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="Z34" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="Z34" s="36" t="s">
+      <c r="AA34" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="AA34" s="36" t="s">
-        <v>154</v>
-      </c>
       <c r="AB34" s="50" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="AC34" s="36" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AD34" s="36" t="s">
-        <v>476</v>
-      </c>
-      <c r="AE34" s="82" t="s">
-        <v>477</v>
+        <v>473</v>
+      </c>
+      <c r="AE34" s="61" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B35" s="87" t="s">
-        <v>119</v>
+      <c r="B35" s="66" t="s">
+        <v>118</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F35" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="H35" s="37">
         <v>1.28</v>
       </c>
       <c r="I35" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J35" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K35" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L35" s="43">
         <v>12.8</v>
       </c>
       <c r="M35" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N35" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O35" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P35" s="38">
         <v>2025</v>
@@ -8576,13 +8550,13 @@
         <v>2039</v>
       </c>
       <c r="S35" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T35" s="39">
         <v>159000000</v>
       </c>
       <c r="U35" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V35" s="28">
         <v>51.1339349</v>
@@ -8591,75 +8565,75 @@
         <v>3.7766611000000001</v>
       </c>
       <c r="X35" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y35" s="36" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="Z35" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA35" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="AA35" s="36" t="s">
-        <v>126</v>
-      </c>
       <c r="AB35" s="50" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="AC35" s="36" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="AD35" s="36" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="AE35" s="55" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
     </row>
     <row r="36" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="B36" s="87" t="s">
-        <v>359</v>
+        <v>185</v>
+      </c>
+      <c r="B36" s="66" t="s">
+        <v>356</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>45</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="H36" s="86">
+        <v>358</v>
+      </c>
+      <c r="H36" s="65">
         <v>5.0046999999999999E-3</v>
       </c>
       <c r="I36" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J36" s="43">
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="K36" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L36" s="52">
         <v>5.0047000000000001E-2</v>
       </c>
       <c r="M36" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="N36" s="86">
+        <v>92</v>
+      </c>
+      <c r="N36" s="65">
         <v>5.1711E-2</v>
       </c>
       <c r="O36" s="31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P36" s="38">
         <v>2026</v>
@@ -8671,13 +8645,13 @@
         <v>2038</v>
       </c>
       <c r="S36" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T36" s="39">
         <v>26498650</v>
       </c>
       <c r="U36" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V36" s="28">
         <v>50.529000000000003</v>
@@ -8686,51 +8660,51 @@
         <v>18.047000000000001</v>
       </c>
       <c r="X36" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y36" s="36" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="Z36" s="36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AA36" s="36" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AB36" s="50" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="AC36" s="36" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AD36" s="36" t="s">
-        <v>627</v>
-      </c>
-      <c r="AE36" s="81" t="s">
-        <v>628</v>
+        <v>623</v>
+      </c>
+      <c r="AE36" s="60" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B37" s="87" t="s">
-        <v>423</v>
+      <c r="B37" s="66" t="s">
+        <v>420</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" s="36" t="s">
         <v>112</v>
-      </c>
-      <c r="D37" s="36" t="s">
-        <v>113</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>50</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H37" s="37">
         <v>0.68</v>
@@ -8742,7 +8716,7 @@
         <v>1.9</v>
       </c>
       <c r="K37" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L37" s="43">
         <v>6.8</v>
@@ -8754,7 +8728,7 @@
         <v>19</v>
       </c>
       <c r="O37" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P37" s="38">
         <v>2025</v>
@@ -8766,13 +8740,13 @@
         <v>2039</v>
       </c>
       <c r="S37" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T37" s="39">
         <v>234000000</v>
       </c>
       <c r="U37" s="39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V37" s="28">
         <v>38.129899999999999</v>
@@ -8781,48 +8755,48 @@
         <v>23.527000000000001</v>
       </c>
       <c r="X37" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y37" s="36" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="Z37" s="36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AA37" s="36" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AB37" s="50" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AC37" s="36" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="AD37" s="36" t="s">
-        <v>520</v>
-      </c>
-      <c r="AE37" s="80" t="s">
-        <v>502</v>
+        <v>516</v>
+      </c>
+      <c r="AE37" s="59" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="B38" s="88" t="s">
-        <v>396</v>
+        <v>148</v>
+      </c>
+      <c r="B38" s="67" t="s">
+        <v>393</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D38" s="36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="33">
@@ -8835,7 +8809,7 @@
         <v>0.2</v>
       </c>
       <c r="K38" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L38" s="42">
         <v>2</v>
@@ -8847,7 +8821,7 @@
         <v>2</v>
       </c>
       <c r="O38" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P38" s="34">
         <v>2025</v>
@@ -8859,7 +8833,7 @@
         <v>2038</v>
       </c>
       <c r="S38" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T38" s="35">
         <v>54000000</v>
@@ -8874,51 +8848,51 @@
         <v>12.7671053619066</v>
       </c>
       <c r="X38" s="23" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y38" s="32" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="Z38" s="32" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="AA38" s="32" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AB38" s="50" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="AC38" s="32" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="AD38" s="32" t="s">
-        <v>514</v>
-      </c>
-      <c r="AE38" s="55" t="s">
-        <v>27</v>
+        <v>510</v>
+      </c>
+      <c r="AE38" s="59" t="s">
+        <v>498</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:31" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="88" t="s">
+      <c r="B39" s="67" t="s">
+        <v>258</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>260</v>
-      </c>
       <c r="D39" s="32" t="s">
-        <v>261</v>
+        <v>445</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>50</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H39" s="33">
         <v>0.85799999999999998</v>
@@ -8954,13 +8928,13 @@
         <v>2039</v>
       </c>
       <c r="S39" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T39" s="35">
         <v>127000000</v>
       </c>
       <c r="U39" s="39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V39" s="25">
         <v>37.916800000000002</v>
@@ -8969,27 +8943,27 @@
         <v>23.069400000000002</v>
       </c>
       <c r="X39" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y39" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z39" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="AA39" s="32" t="s">
         <v>263</v>
       </c>
-      <c r="Z39" s="32" t="s">
+      <c r="AB39" s="50" t="s">
         <v>264</v>
       </c>
-      <c r="AA39" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="AB39" s="50" t="s">
-        <v>266</v>
-      </c>
       <c r="AC39" s="32" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="AD39" s="32" t="s">
-        <v>633</v>
-      </c>
-      <c r="AE39" s="80" t="s">
+        <v>629</v>
+      </c>
+      <c r="AE39" s="59" t="s">
         <v>23</v>
       </c>
     </row>
@@ -8997,23 +8971,23 @@
       <c r="A40" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="88" t="s">
+      <c r="B40" s="67" t="s">
         <v>88</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D40" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F40" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="H40" s="33">
         <v>1.4</v>
@@ -9025,7 +8999,7 @@
         <v>1.4</v>
       </c>
       <c r="K40" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L40" s="42">
         <v>14</v>
@@ -9037,7 +9011,7 @@
         <v>14</v>
       </c>
       <c r="O40" s="42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P40" s="34">
         <v>2020</v>
@@ -9049,7 +9023,7 @@
         <v>2039</v>
       </c>
       <c r="S40" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T40" s="35">
         <v>356900000</v>
@@ -9064,53 +9038,53 @@
         <v>4.2713660000000004</v>
       </c>
       <c r="X40" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y40" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="Y40" s="32" t="s">
+      <c r="Z40" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="Z40" s="32" t="s">
+      <c r="AA40" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="AA40" s="32" t="s">
-        <v>99</v>
-      </c>
       <c r="AB40" s="50" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="AC40" s="32" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="AD40" s="32" t="s">
-        <v>635</v>
-      </c>
-      <c r="AE40" s="84" t="s">
+        <v>631</v>
+      </c>
+      <c r="AE40" s="63" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="B41" s="87" t="s">
-        <v>641</v>
+        <v>185</v>
+      </c>
+      <c r="B41" s="66" t="s">
+        <v>637</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D41" s="36" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>58</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="H41" s="86">
+        <v>398</v>
+      </c>
+      <c r="H41" s="65">
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="I41" s="43">
@@ -9120,7 +9094,7 @@
         <v>0.16</v>
       </c>
       <c r="K41" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L41" s="37">
         <v>0.46373999999999999</v>
@@ -9132,7 +9106,7 @@
         <v>1.6</v>
       </c>
       <c r="O41" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P41" s="38">
         <v>2024</v>
@@ -9144,13 +9118,13 @@
         <v>2038</v>
       </c>
       <c r="S41" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T41" s="39">
         <v>29500000</v>
       </c>
       <c r="U41" s="39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V41" s="22">
         <v>60.618241659279597</v>
@@ -9159,25 +9133,25 @@
         <v>16.891107915855802</v>
       </c>
       <c r="X41" s="22" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Y41" s="36" t="s">
+        <v>635</v>
+      </c>
+      <c r="Z41" s="36" t="s">
+        <v>636</v>
+      </c>
+      <c r="AA41" s="36" t="s">
+        <v>399</v>
+      </c>
+      <c r="AB41" s="50" t="s">
+        <v>638</v>
+      </c>
+      <c r="AC41" s="36" t="s">
         <v>639</v>
       </c>
-      <c r="Z41" s="36" t="s">
+      <c r="AD41" s="36" t="s">
         <v>640</v>
-      </c>
-      <c r="AA41" s="36" t="s">
-        <v>402</v>
-      </c>
-      <c r="AB41" s="50" t="s">
-        <v>642</v>
-      </c>
-      <c r="AC41" s="36" t="s">
-        <v>643</v>
-      </c>
-      <c r="AD41" s="36" t="s">
-        <v>644</v>
       </c>
       <c r="AE41" s="55" t="s">
         <v>25</v>
@@ -9187,23 +9161,23 @@
       <c r="A42" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B42" s="87" t="s">
-        <v>142</v>
+      <c r="B42" s="66" t="s">
+        <v>141</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="32" t="s">
         <v>112</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>113</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>53</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H42" s="37">
         <v>0.36599999999999999</v>
@@ -9215,7 +9189,7 @@
         <v>0.36599999999999999</v>
       </c>
       <c r="K42" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L42" s="43">
         <v>3.7</v>
@@ -9227,7 +9201,7 @@
         <v>3.66</v>
       </c>
       <c r="O42" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P42" s="38">
         <v>2023</v>
@@ -9239,13 +9213,13 @@
         <v>2038</v>
       </c>
       <c r="S42" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T42" s="39">
         <v>117000000</v>
       </c>
       <c r="U42" s="39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V42" s="28">
         <v>44.968299999999999</v>
@@ -9254,75 +9228,75 @@
         <v>14.1221</v>
       </c>
       <c r="X42" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y42" s="36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Z42" s="36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AA42" s="36" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AB42" s="50" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="AC42" s="36" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="AD42" s="36" t="s">
-        <v>509</v>
-      </c>
-      <c r="AE42" s="80" t="s">
-        <v>511</v>
+        <v>505</v>
+      </c>
+      <c r="AE42" s="59" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="43" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B43" s="87" t="s">
-        <v>482</v>
+      <c r="B43" s="66" t="s">
+        <v>479</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="D43" s="36" t="s">
-        <v>484</v>
+        <v>480</v>
+      </c>
+      <c r="D43" s="32" t="s">
+        <v>317</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I43" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J43" s="43">
         <v>5</v>
       </c>
       <c r="K43" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L43" s="53">
         <v>31.381101000000001</v>
       </c>
       <c r="M43" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N43" s="43">
         <v>50</v>
       </c>
       <c r="O43" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P43" s="38">
         <v>2025</v>
@@ -9334,13 +9308,13 @@
         <v>2039</v>
       </c>
       <c r="S43" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T43" s="39">
         <v>118000000</v>
       </c>
       <c r="U43" s="39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V43" s="28">
         <v>51.976999999999997</v>
@@ -9349,51 +9323,51 @@
         <v>4.05</v>
       </c>
       <c r="X43" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y43" s="36" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Z43" s="36" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AA43" s="36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB43" s="51" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="AC43" s="36" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="AD43" s="36" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="AE43" s="54" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="44" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" s="66" t="s">
         <v>134</v>
       </c>
-      <c r="B44" s="87" t="s">
-        <v>135</v>
-      </c>
       <c r="C44" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H44" s="37">
         <v>7.0000000000000007E-2</v>
@@ -9405,7 +9379,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="K44" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L44" s="43">
         <v>0.7</v>
@@ -9417,7 +9391,7 @@
         <v>0.7</v>
       </c>
       <c r="O44" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P44" s="38">
         <v>2026</v>
@@ -9429,13 +9403,13 @@
         <v>2041</v>
       </c>
       <c r="S44" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T44" s="39">
         <v>36000000</v>
       </c>
       <c r="U44" s="39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V44" s="28">
         <v>50.406342306737002</v>
@@ -9444,75 +9418,75 @@
         <v>4.6321740189769196</v>
       </c>
       <c r="X44" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y44" s="36" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="Z44" s="36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AA44" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AB44" s="50" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="AC44" s="36" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="AD44" s="36" t="s">
-        <v>648</v>
-      </c>
-      <c r="AE44" s="81" t="s">
-        <v>606</v>
+        <v>644</v>
+      </c>
+      <c r="AE44" s="60" t="s">
+        <v>602</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:31" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="B45" s="87" t="s">
-        <v>335</v>
+        <v>185</v>
+      </c>
+      <c r="B45" s="66" t="s">
+        <v>332</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D45" s="36" t="s">
-        <v>650</v>
+        <v>266</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H45" s="37">
         <v>0.04</v>
       </c>
       <c r="I45" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J45" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K45" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L45" s="37">
         <v>0.41452</v>
       </c>
       <c r="M45" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N45" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O45" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P45" s="38">
         <v>2025</v>
@@ -9524,13 +9498,13 @@
         <v>2038</v>
       </c>
       <c r="S45" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T45" s="39">
         <v>13000000</v>
       </c>
       <c r="U45" s="39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V45" s="22">
         <v>59.2181</v>
@@ -9539,27 +9513,27 @@
         <v>10.9298</v>
       </c>
       <c r="X45" s="22" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Y45" s="36" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="Z45" s="36" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="AA45" s="36" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AB45" s="50" t="s">
+        <v>645</v>
+      </c>
+      <c r="AC45" s="36" t="s">
         <v>649</v>
       </c>
-      <c r="AC45" s="36" t="s">
-        <v>654</v>
-      </c>
       <c r="AD45" s="36" t="s">
-        <v>655</v>
-      </c>
-      <c r="AE45" s="80" t="s">
+        <v>650</v>
+      </c>
+      <c r="AE45" s="59" t="s">
         <v>23</v>
       </c>
     </row>
@@ -9567,26 +9541,26 @@
       <c r="A46" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B46" s="89" t="s">
-        <v>253</v>
+      <c r="B46" s="68" t="s">
+        <v>252</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" s="32" t="s">
         <v>112</v>
-      </c>
-      <c r="D46" s="32" t="s">
-        <v>113</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>50</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H46" s="33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I46" s="42">
         <v>1</v>
@@ -9595,9 +9569,9 @@
         <v>1</v>
       </c>
       <c r="K46" s="42" t="s">
-        <v>93</v>
-      </c>
-      <c r="L46" s="77">
+        <v>92</v>
+      </c>
+      <c r="L46" s="56">
         <v>6.8833489999999999</v>
       </c>
       <c r="M46" s="42">
@@ -9607,7 +9581,7 @@
         <v>10</v>
       </c>
       <c r="O46" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P46" s="34">
         <v>2024</v>
@@ -9619,7 +9593,7 @@
         <v>2039</v>
       </c>
       <c r="S46" s="23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T46" s="35">
         <v>124268490</v>
@@ -9634,51 +9608,51 @@
         <v>24.060400000000001</v>
       </c>
       <c r="X46" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y46" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="Z46" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA46" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="Z46" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA46" s="32" t="s">
-        <v>256</v>
-      </c>
       <c r="AB46" s="50" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="AC46" s="32" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="AD46" s="32" t="s">
-        <v>517</v>
-      </c>
-      <c r="AE46" s="80" t="s">
+        <v>513</v>
+      </c>
+      <c r="AE46" s="59" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B47" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D47" s="32" t="s">
         <v>169</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D47" s="32" t="s">
-        <v>170</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H47" s="33"/>
       <c r="I47" s="42"/>
@@ -9698,7 +9672,7 @@
         <v>2038</v>
       </c>
       <c r="S47" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T47" s="35">
         <v>40000000</v>
@@ -9713,25 +9687,25 @@
         <v>24.47278</v>
       </c>
       <c r="X47" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y47" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z47" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="Z47" s="32" t="s">
+      <c r="AA47" s="32" t="s">
         <v>173</v>
-      </c>
-      <c r="AA47" s="32" t="s">
-        <v>174</v>
       </c>
       <c r="AB47" s="2"/>
       <c r="AC47" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="AD47" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="AD47" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="AE47" s="81" t="s">
+      <c r="AE47" s="60" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9740,22 +9714,22 @@
         <v>87</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D48" s="36" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>58</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H48" s="37">
         <v>0.5</v>
@@ -9764,7 +9738,7 @@
         <v>0.40600000000000003</v>
       </c>
       <c r="J48" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K48" s="43">
         <v>0.40600000000000003</v>
@@ -9776,7 +9750,7 @@
         <v>4.0599999999999996</v>
       </c>
       <c r="N48" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O48" s="43">
         <v>4.0599999999999996</v>
@@ -9791,13 +9765,13 @@
         <v>2037</v>
       </c>
       <c r="S48" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T48" s="39">
         <v>97000000</v>
       </c>
       <c r="U48" s="39" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="V48" s="22">
         <v>58.099057767351503</v>
@@ -9806,51 +9780,51 @@
         <v>11.861499508001399</v>
       </c>
       <c r="X48" s="22" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Y48" s="36" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="Z48" s="36" t="s">
+        <v>437</v>
+      </c>
+      <c r="AA48" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="AB48" s="51" t="s">
         <v>440</v>
       </c>
-      <c r="AA48" s="36" t="s">
-        <v>395</v>
-      </c>
-      <c r="AB48" s="51" t="s">
-        <v>443</v>
-      </c>
       <c r="AC48" s="36" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="AD48" s="36" t="s">
-        <v>442</v>
-      </c>
-      <c r="AE48" s="80" t="s">
+        <v>439</v>
+      </c>
+      <c r="AE48" s="59" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B49" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="D49" s="36" t="s">
         <v>161</v>
-      </c>
-      <c r="D49" s="36" t="s">
-        <v>162</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>54</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H49" s="37"/>
       <c r="I49" s="43"/>
@@ -9870,7 +9844,7 @@
         <v>2038</v>
       </c>
       <c r="S49" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T49" s="39">
         <v>55000000</v>
@@ -9885,44 +9859,44 @@
         <v>9.3382000000000005</v>
       </c>
       <c r="X49" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y49" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z49" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="Z49" s="36" t="s">
+      <c r="AA49" s="36" t="s">
         <v>165</v>
-      </c>
-      <c r="AA49" s="36" t="s">
-        <v>166</v>
       </c>
       <c r="AB49" s="4"/>
       <c r="AC49" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="AD49" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="AD49" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE49" s="81" t="s">
+      <c r="AE49" s="60" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="22"/>
       <c r="B50" s="44" t="s">
+        <v>244</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D50" s="36" t="s">
         <v>245</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D50" s="36" t="s">
-        <v>246</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="37"/>
@@ -9943,7 +9917,7 @@
         <v>2038</v>
       </c>
       <c r="S50" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T50" s="39">
         <v>62000000</v>
@@ -9958,23 +9932,23 @@
         <v>10.948</v>
       </c>
       <c r="X50" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y50" s="36" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z50" s="36" t="s">
         <v>248</v>
       </c>
-      <c r="Z50" s="36" t="s">
+      <c r="AA50" s="36" t="s">
         <v>249</v>
-      </c>
-      <c r="AA50" s="36" t="s">
-        <v>250</v>
       </c>
       <c r="AB50" s="4"/>
       <c r="AC50" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="AD50" s="36" t="s">
         <v>251</v>
-      </c>
-      <c r="AD50" s="36" t="s">
-        <v>252</v>
       </c>
       <c r="AE50" s="54" t="s">
         <v>27</v>
@@ -9982,25 +9956,25 @@
     </row>
     <row r="51" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F51" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G51" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="H51" s="33"/>
       <c r="I51" s="42"/>
@@ -10020,7 +9994,7 @@
         <v>2039</v>
       </c>
       <c r="S51" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T51" s="35">
         <v>40000000</v>
@@ -10035,25 +10009,25 @@
         <v>-0.80400000000000005</v>
       </c>
       <c r="X51" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y51" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z51" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA51" s="32" t="s">
         <v>212</v>
-      </c>
-      <c r="Z51" s="32" t="s">
-        <v>207</v>
-      </c>
-      <c r="AA51" s="32" t="s">
-        <v>213</v>
       </c>
       <c r="AB51" s="2"/>
       <c r="AC51" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD51" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="AD51" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="AE51" s="81" t="s">
+      <c r="AE51" s="60" t="s">
         <v>21</v>
       </c>
     </row>
@@ -10062,22 +10036,22 @@
         <v>87</v>
       </c>
       <c r="B52" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>178</v>
-      </c>
       <c r="D52" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H52" s="37">
         <v>0.4</v>
@@ -10089,7 +10063,7 @@
         <v>0.4</v>
       </c>
       <c r="K52" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L52" s="43">
         <v>4</v>
@@ -10101,7 +10075,7 @@
         <v>4</v>
       </c>
       <c r="O52" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P52" s="38">
         <v>2022</v>
@@ -10113,13 +10087,13 @@
         <v>2035</v>
       </c>
       <c r="S52" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T52" s="39">
         <v>88286266</v>
       </c>
       <c r="U52" s="39" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V52" s="28">
         <v>60.306100000000001</v>
@@ -10128,51 +10102,51 @@
         <v>25.498100000000001</v>
       </c>
       <c r="X52" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y52" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="Z52" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="Z52" s="36" t="s">
+      <c r="AA52" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AA52" s="36" t="s">
+      <c r="AB52" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="AB52" s="29" t="s">
+      <c r="AC52" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="AC52" s="36" t="s">
+      <c r="AD52" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="AD52" s="36" t="s">
-        <v>185</v>
-      </c>
       <c r="AE52" s="55" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="53" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H53" s="33"/>
       <c r="I53" s="42">
@@ -10182,7 +10156,7 @@
         <v>0.04</v>
       </c>
       <c r="K53" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L53" s="42">
         <v>0.15</v>
@@ -10194,7 +10168,7 @@
         <v>0.4</v>
       </c>
       <c r="O53" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P53" s="34">
         <v>2021</v>
@@ -10206,7 +10180,7 @@
         <v>2028</v>
       </c>
       <c r="S53" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T53" s="35">
         <v>3867988</v>
@@ -10221,48 +10195,48 @@
         <v>-21.401</v>
       </c>
       <c r="X53" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y53" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z53" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="AA53" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="AB53" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="Z53" s="32" t="s">
+      <c r="AC53" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="AA53" s="32" t="s">
+      <c r="AD53" s="32" t="s">
         <v>290</v>
       </c>
-      <c r="AB53" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="AC53" s="32" t="s">
-        <v>292</v>
-      </c>
-      <c r="AD53" s="32" t="s">
-        <v>293</v>
-      </c>
-      <c r="AE53" s="82" t="s">
+      <c r="AE53" s="61" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="33"/>
@@ -10283,7 +10257,7 @@
         <v>2033</v>
       </c>
       <c r="S54" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T54" s="35">
         <v>35000000</v>
@@ -10298,25 +10272,25 @@
         <v>6.84</v>
       </c>
       <c r="X54" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y54" s="32" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="Z54" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AA54" s="32" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AB54" s="2"/>
       <c r="AC54" s="32" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AD54" s="32" t="s">
-        <v>350</v>
-      </c>
-      <c r="AE54" s="81" t="s">
+        <v>347</v>
+      </c>
+      <c r="AE54" s="60" t="s">
         <v>21</v>
       </c>
     </row>
@@ -10325,34 +10299,34 @@
         <v>87</v>
       </c>
       <c r="B55" s="24" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H55" s="33">
         <v>4.2750000000000004</v>
       </c>
       <c r="I55" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J55" s="42">
         <v>4.2750000000000004</v>
       </c>
       <c r="K55" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L55" s="42">
         <v>42.75</v>
@@ -10362,7 +10336,7 @@
         <v>42.75</v>
       </c>
       <c r="O55" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P55" s="34">
         <v>2025</v>
@@ -10374,13 +10348,13 @@
         <v>2039</v>
       </c>
       <c r="S55" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T55" s="35">
         <v>225000000</v>
       </c>
       <c r="U55" s="35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="V55" s="23">
         <v>57.788622470324199</v>
@@ -10389,23 +10363,23 @@
         <v>4.4366416948962097</v>
       </c>
       <c r="X55" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y55" s="32" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="Z55" s="32" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AA55" s="32"/>
       <c r="AB55" s="26" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AC55" s="32" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="AD55" s="32" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="AE55" s="55" t="s">
         <v>25</v>
@@ -10413,25 +10387,25 @@
     </row>
     <row r="56" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H56" s="33">
         <v>0.1</v>
@@ -10440,7 +10414,7 @@
         <v>0.1</v>
       </c>
       <c r="J56" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K56" s="42">
         <v>0.1</v>
@@ -10452,7 +10426,7 @@
         <v>1</v>
       </c>
       <c r="N56" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O56" s="42">
         <v>1</v>
@@ -10467,7 +10441,7 @@
         <v>2038</v>
       </c>
       <c r="S56" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T56" s="35">
         <v>38000000</v>
@@ -10482,25 +10456,25 @@
         <v>-2.0750000000000002</v>
       </c>
       <c r="X56" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y56" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="Z56" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="Z56" s="32" t="s">
+      <c r="AA56" s="32" t="s">
         <v>224</v>
-      </c>
-      <c r="AA56" s="32" t="s">
-        <v>225</v>
       </c>
       <c r="AB56" s="2"/>
       <c r="AC56" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="AD56" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="AD56" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="AE56" s="81" t="s">
+      <c r="AE56" s="60" t="s">
         <v>21</v>
       </c>
     </row>
@@ -10509,19 +10483,19 @@
         <v>87</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>268</v>
+        <v>480</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="33">
@@ -10534,7 +10508,7 @@
         <v>2</v>
       </c>
       <c r="K57" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L57" s="42">
         <v>54</v>
@@ -10546,7 +10520,7 @@
         <v>54</v>
       </c>
       <c r="O57" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P57" s="34">
         <v>2025</v>
@@ -10558,7 +10532,7 @@
         <v>2057</v>
       </c>
       <c r="S57" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T57" s="35">
         <v>205000000</v>
@@ -10573,51 +10547,51 @@
         <v>1.2444999999999999</v>
       </c>
       <c r="X57" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y57" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="Z57" s="32" t="s">
+        <v>379</v>
+      </c>
+      <c r="AA57" s="32" t="s">
+        <v>380</v>
+      </c>
+      <c r="AB57" s="26" t="s">
         <v>381</v>
       </c>
-      <c r="Z57" s="32" t="s">
+      <c r="AC57" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="AA57" s="32" t="s">
+      <c r="AD57" s="32" t="s">
         <v>383</v>
       </c>
-      <c r="AB57" s="26" t="s">
-        <v>384</v>
-      </c>
-      <c r="AC57" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="AD57" s="32" t="s">
-        <v>386</v>
-      </c>
-      <c r="AE57" s="80" t="s">
+      <c r="AE57" s="59" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>50</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H58" s="33"/>
       <c r="I58" s="42"/>
@@ -10637,7 +10611,7 @@
         <v>2038</v>
       </c>
       <c r="S58" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T58" s="35">
         <v>30000000</v>
@@ -10652,25 +10626,25 @@
         <v>22.896100000000001</v>
       </c>
       <c r="X58" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y58" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="Z58" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="AA58" s="32" t="s">
         <v>276</v>
-      </c>
-      <c r="Z58" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA58" s="32" t="s">
-        <v>278</v>
       </c>
       <c r="AB58" s="2"/>
       <c r="AC58" s="32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AD58" s="32" t="s">
-        <v>280</v>
-      </c>
-      <c r="AE58" s="81" t="s">
+        <v>278</v>
+      </c>
+      <c r="AE58" s="60" t="s">
         <v>21</v>
       </c>
     </row>
@@ -10679,19 +10653,19 @@
         <v>87</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D59" s="36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="37">
@@ -10701,7 +10675,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="J59" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K59" s="43">
         <v>5.6000000000000001E-2</v>
@@ -10713,7 +10687,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="N59" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O59" s="43">
         <v>0.56000000000000005</v>
@@ -10728,7 +10702,7 @@
         <v>2037</v>
       </c>
       <c r="S59" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T59" s="39">
         <v>49000000</v>
@@ -10739,49 +10713,49 @@
       <c r="V59" s="22"/>
       <c r="W59" s="22"/>
       <c r="X59" s="22" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Y59" s="36"/>
       <c r="Z59" s="36" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AA59" s="36" t="s">
+        <v>372</v>
+      </c>
+      <c r="AB59" s="29" t="s">
+        <v>373</v>
+      </c>
+      <c r="AC59" s="36" t="s">
+        <v>374</v>
+      </c>
+      <c r="AD59" s="36" t="s">
         <v>375</v>
       </c>
-      <c r="AB59" s="29" t="s">
-        <v>376</v>
-      </c>
-      <c r="AC59" s="36" t="s">
-        <v>377</v>
-      </c>
-      <c r="AD59" s="36" t="s">
-        <v>378</v>
-      </c>
-      <c r="AE59" s="80" t="s">
+      <c r="AE59" s="59" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:31" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C60" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D60" s="36" t="s">
         <v>112</v>
-      </c>
-      <c r="D60" s="36" t="s">
-        <v>113</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>42</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H60" s="37">
         <v>1.2</v>
@@ -10793,7 +10767,7 @@
         <v>1.2</v>
       </c>
       <c r="K60" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L60" s="43">
         <v>12</v>
@@ -10805,7 +10779,7 @@
         <v>12</v>
       </c>
       <c r="O60" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P60" s="38">
         <v>2025</v>
@@ -10817,7 +10791,7 @@
         <v>2040</v>
       </c>
       <c r="S60" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T60" s="39">
         <v>260000000</v>
@@ -10832,49 +10806,49 @@
         <v>5.3994999999999997</v>
       </c>
       <c r="X60" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y60" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z60" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA60" s="36" t="s">
         <v>218</v>
-      </c>
-      <c r="Z60" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA60" s="36" t="s">
-        <v>219</v>
       </c>
       <c r="AB60" s="4"/>
       <c r="AC60" s="36" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="AD60" s="36" t="s">
-        <v>220</v>
-      </c>
-      <c r="AE60" s="81" t="s">
+        <v>219</v>
+      </c>
+      <c r="AE60" s="60" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:31" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D61" s="36" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H61" s="37"/>
       <c r="I61" s="43"/>
@@ -10894,7 +10868,7 @@
         <v>2038</v>
       </c>
       <c r="S61" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T61" s="39">
         <v>35000000</v>
@@ -10909,23 +10883,23 @@
         <v>22.126007672556039</v>
       </c>
       <c r="X61" s="22" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Y61" s="36"/>
       <c r="Z61" s="36" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AA61" s="36" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AB61" s="4"/>
       <c r="AC61" s="36" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AD61" s="36" t="s">
-        <v>345</v>
-      </c>
-      <c r="AE61" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="AE61" s="60" t="s">
         <v>21</v>
       </c>
     </row>
@@ -11005,151 +10979,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="70" t="s">
-        <v>403</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="A1" s="83" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="56" t="s">
-        <v>404</v>
-      </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
+      <c r="A3" s="69" t="s">
+        <v>401</v>
+      </c>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="76" t="s">
-        <v>405</v>
-      </c>
-      <c r="B4" s="60"/>
-      <c r="C4" s="65" t="s">
-        <v>406</v>
-      </c>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
+      <c r="A4" s="89" t="s">
+        <v>402</v>
+      </c>
+      <c r="B4" s="73"/>
+      <c r="C4" s="78" t="s">
+        <v>403</v>
+      </c>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="65" t="s">
-        <v>407</v>
-      </c>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="78" t="s">
+        <v>404</v>
+      </c>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="65" t="s">
-        <v>408</v>
-      </c>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="78" t="s">
+        <v>405</v>
+      </c>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="72" t="s">
+      <c r="A7" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="60"/>
-      <c r="C7" s="65" t="s">
-        <v>409</v>
-      </c>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
+      <c r="B7" s="73"/>
+      <c r="C7" s="78" t="s">
+        <v>406</v>
+      </c>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="65" t="s">
-        <v>410</v>
-      </c>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
+      <c r="B8" s="73"/>
+      <c r="C8" s="78" t="s">
+        <v>407</v>
+      </c>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="65" t="s">
-        <v>411</v>
-      </c>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
+      <c r="B9" s="73"/>
+      <c r="C9" s="78" t="s">
+        <v>408</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="60"/>
-      <c r="C10" s="65" t="s">
-        <v>412</v>
-      </c>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="78" t="s">
+        <v>409</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="56" t="s">
-        <v>413</v>
-      </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
+      <c r="A12" s="69" t="s">
+        <v>410</v>
+      </c>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="67" t="s">
-        <v>414</v>
-      </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="65" t="s">
-        <v>415</v>
-      </c>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
+      <c r="A13" s="80" t="s">
+        <v>411</v>
+      </c>
+      <c r="B13" s="73"/>
+      <c r="C13" s="78" t="s">
+        <v>412</v>
+      </c>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="74" t="s">
-        <v>416</v>
-      </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="65" t="s">
-        <v>417</v>
-      </c>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
+      <c r="A14" s="87" t="s">
+        <v>413</v>
+      </c>
+      <c r="B14" s="73"/>
+      <c r="C14" s="78" t="s">
+        <v>414</v>
+      </c>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="69" t="s">
-        <v>418</v>
-      </c>
-      <c r="B15" s="60"/>
-      <c r="C15" s="65" t="s">
-        <v>419</v>
-      </c>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
+      <c r="A15" s="82" t="s">
+        <v>415</v>
+      </c>
+      <c r="B15" s="73"/>
+      <c r="C15" s="78" t="s">
+        <v>416</v>
+      </c>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="46"/>
       <c r="B19" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>

--- a/excel_data/Innovation_Fund_Projects_data - 290326.xlsx
+++ b/excel_data/Innovation_Fund_Projects_data - 290326.xlsx
@@ -4370,36 +4370,27 @@
     <xf numFmtId="0" fontId="20" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4421,6 +4412,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4742,40 +4742,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="4" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
     </row>
     <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -4792,12 +4792,12 @@
       <c r="B6" s="3">
         <v>62</v>
       </c>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
@@ -4806,12 +4806,12 @@
       <c r="B7" s="5">
         <v>16</v>
       </c>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -4820,12 +4820,12 @@
       <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
@@ -4834,12 +4834,12 @@
       <c r="B9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -4848,12 +4848,12 @@
       <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
     </row>
     <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
@@ -4862,12 +4862,12 @@
       <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -4876,24 +4876,24 @@
       <c r="B12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
     </row>
     <row r="15" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="69" t="s">
+      <c r="A15" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="70"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
     </row>
     <row r="16" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -4905,11 +4905,11 @@
       <c r="C16" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="72"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="73"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="71"/>
     </row>
     <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
@@ -4918,14 +4918,14 @@
       <c r="B17" s="9">
         <v>21</v>
       </c>
-      <c r="C17" s="71" t="s">
+      <c r="C17" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="72"/>
-      <c r="E17" s="72"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="73"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="71"/>
     </row>
     <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
@@ -4934,14 +4934,14 @@
       <c r="B18" s="11">
         <v>20</v>
       </c>
-      <c r="C18" s="75" t="s">
+      <c r="C18" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="73"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="71"/>
     </row>
     <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
@@ -4950,14 +4950,14 @@
       <c r="B19" s="13">
         <v>10</v>
       </c>
-      <c r="C19" s="71" t="s">
+      <c r="C19" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="73"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="71"/>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
@@ -4966,14 +4966,14 @@
       <c r="B20" s="15">
         <v>4</v>
       </c>
-      <c r="C20" s="75" t="s">
+      <c r="C20" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="73"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="71"/>
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
@@ -4982,14 +4982,14 @@
       <c r="B21" s="17">
         <v>3</v>
       </c>
-      <c r="C21" s="71" t="s">
+      <c r="C21" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="73"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="71"/>
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
@@ -4998,14 +4998,14 @@
       <c r="B22" s="17">
         <v>1</v>
       </c>
-      <c r="C22" s="75" t="s">
+      <c r="C22" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="73"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="71"/>
     </row>
     <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
@@ -5014,14 +5014,14 @@
       <c r="B23" s="17">
         <v>1</v>
       </c>
-      <c r="C23" s="71" t="s">
+      <c r="C23" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="73"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="71"/>
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
@@ -5030,14 +5030,14 @@
       <c r="B24" s="19">
         <v>1</v>
       </c>
-      <c r="C24" s="75" t="s">
+      <c r="C24" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="73"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="71"/>
     </row>
     <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
@@ -5046,26 +5046,26 @@
       <c r="B25" s="21">
         <v>1</v>
       </c>
-      <c r="C25" s="71" t="s">
+      <c r="C25" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="73"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="71"/>
     </row>
     <row r="28" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="69" t="s">
+      <c r="A28" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="70"/>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="70"/>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
     </row>
     <row r="29" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
@@ -5209,12 +5209,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C23:H23"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="A1:H1"/>
@@ -5231,6 +5225,12 @@
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C23:H23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10979,141 +10979,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="80" t="s">
         <v>400</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="74" t="s">
         <v>401</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="86" t="s">
         <v>402</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="78" t="s">
+      <c r="B4" s="71"/>
+      <c r="C4" s="79" t="s">
         <v>403</v>
       </c>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="78" t="s">
+      <c r="B5" s="71"/>
+      <c r="C5" s="79" t="s">
         <v>404</v>
       </c>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="73"/>
-      <c r="C6" s="78" t="s">
+      <c r="B6" s="71"/>
+      <c r="C6" s="79" t="s">
         <v>405</v>
       </c>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="78" t="s">
+      <c r="B7" s="71"/>
+      <c r="C7" s="79" t="s">
         <v>406</v>
       </c>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88" t="s">
+      <c r="A8" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="73"/>
-      <c r="C8" s="78" t="s">
+      <c r="B8" s="71"/>
+      <c r="C8" s="79" t="s">
         <v>407</v>
       </c>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="73"/>
-      <c r="C9" s="78" t="s">
+      <c r="B9" s="71"/>
+      <c r="C9" s="79" t="s">
         <v>408</v>
       </c>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="79" t="s">
+      <c r="A10" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="73"/>
-      <c r="C10" s="78" t="s">
+      <c r="B10" s="71"/>
+      <c r="C10" s="79" t="s">
         <v>409</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="69" t="s">
+      <c r="A12" s="74" t="s">
         <v>410</v>
       </c>
-      <c r="B12" s="70"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="80" t="s">
+      <c r="A13" s="88" t="s">
         <v>411</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="78" t="s">
+      <c r="B13" s="71"/>
+      <c r="C13" s="79" t="s">
         <v>412</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="87" t="s">
+      <c r="A14" s="84" t="s">
         <v>413</v>
       </c>
-      <c r="B14" s="73"/>
-      <c r="C14" s="78" t="s">
+      <c r="B14" s="71"/>
+      <c r="C14" s="79" t="s">
         <v>414</v>
       </c>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="82" t="s">
+      <c r="A15" s="78" t="s">
         <v>415</v>
       </c>
-      <c r="B15" s="73"/>
-      <c r="C15" s="78" t="s">
+      <c r="B15" s="71"/>
+      <c r="C15" s="79" t="s">
         <v>416</v>
       </c>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
@@ -11128,6 +11128,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C10:E10"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="A1:E1"/>
@@ -11144,13 +11151,6 @@
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -11158,6 +11158,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ba695df1-2cef-45b3-b38e-525c8136ab22" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100052CBA820BEBCD468114CF62615C95D9" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="41d93ad2b4fecab14cfdaed9255371f8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ba695df1-2cef-45b3-b38e-525c8136ab22" xmlns:ns3="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="59a815193907c452009623866744c535" ns2:_="" ns3:_="">
     <xsd:import namespace="ba695df1-2cef-45b3-b38e-525c8136ab22"/>
@@ -11398,27 +11418,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51CBE187-A7DE-4A9A-99BE-7485C92477B0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="ba695df1-2cef-45b3-b38e-525c8136ab22"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ba695df1-2cef-45b3-b38e-525c8136ab22" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A39E8DA8-D782-4F69-B46B-77021BF1B166}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82507086-9DCD-4197-A4F6-ECCED658E0D9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11435,29 +11460,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A39E8DA8-D782-4F69-B46B-77021BF1B166}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51CBE187-A7DE-4A9A-99BE-7485C92477B0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="ba695df1-2cef-45b3-b38e-525c8136ab22"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="d75fa1b2-e4ff-4c4f-9d1f-2231fcc7043e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>